--- a/StyleOfDelivery/BCIO-style-hierarchy.xlsx
+++ b/StyleOfDelivery/BCIO-style-hierarchy.xlsx
@@ -442,32 +442,32 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>subontology</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
         </is>
       </c>
     </row>
@@ -524,13 +524,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>continuant</t>
+          <t>occurrent</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -542,21 +542,21 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>generically dependent continuant</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -567,14 +567,14 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BCIO:050552</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -582,7 +582,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>communication channel</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -592,155 +592,176 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+          <t>A &lt;process&gt; by which a communication is delivered.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:050555</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>communication message</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>independent continuant</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>process attribute</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
+          <t>A process profile that is an attribute of a process.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>BCIO:044003</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>communication process attribute</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>An attribute of a communication process.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050554</t>
+          <t>BCIO:044126</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>communication source</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>oral communication pace</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A &lt;material entity&gt; that originates a communication.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OGMS:0000087</t>
+          <t>BCIO:044004</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>extended organism</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>communication style</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
+          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
+          <t>BCIO:050391</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -748,24 +769,32 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>human being</t>
-        </is>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>non-responsive communication style</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
+          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:050553</t>
+          <t>BCIO:044108</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -774,433 +803,462 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>communication recipient</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>interactive communication style</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; who receives a communication.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by being responsive to the recipient's activity.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>interactive presentation</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BCIO:044101</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>occurrent</t>
-        </is>
-      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>empathic communication style</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
+          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>sensitivity, compassion</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BCIO:044089</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>communication style conveying concern</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:050384</t>
+          <t>BCIO:044086</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>cold communication style</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A process involving the transmission of information between two or more participants.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:044061</t>
+          <t>BCIO:050389</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>interrupting</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>direct communication style</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A communication in which one person interjects before another has finished making their point.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by the explicit presentation of information.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Note that this class is different from directive communication style</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:044065</t>
+          <t>BCIO:044097</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>negotiation</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>conversational communication style</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:044011</t>
+          <t>BCIO:044103</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>agenda-sharing communication</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>entertaining communication style</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>agenda mapping</t>
+          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:044023</t>
+          <t>BCIO:044079</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>communication asking permission to provide information and advice</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>active participation encouraging communication style</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
-        </is>
-      </c>
       <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:044040</t>
+          <t>BCIO:050390</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>communication involving elaboration of arguments</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>humorous communication style</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style intended to amuse.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:044078</t>
+          <t>BCIO:044112</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>shifting focus of communication</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>non-judgmental communication style</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:044010</t>
+          <t>BCIO:044099</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>affirming communication</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>directive communication style</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style intended to play an active role in another person's decision making.</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Making explicit statements of partnership or support; Shows approval;</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>Note that this class is different from direct communication style</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:044036</t>
+          <t>BCIO:044118</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>responsive communication style</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>From Motivational Interviewing</t>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:044037</t>
+          <t>BCIO:044116</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>communication involving agreement</t>
-        </is>
-      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>relaxed communication style</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A communication in which one participant concurs with the views stated by another.</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>A communication style characterised by a lack of tension or anxiety.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>calm communication style</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:044038</t>
+          <t>BCIO:044110</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1208,74 +1266,74 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>communication involving agreement followed by highlighting incongruent aspects</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>non-defensive communication style</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>"agreement with a twist" in motivational interviewing</t>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:044019</t>
+          <t>BCIO:044084</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>discussion</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>autonomy-supportive communication style</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>needs-supportive communication style</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>from Self-Determination Theory interventions.</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:044020</t>
+          <t>BCIO:044106</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1283,285 +1341,286 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>classroom-style discussion</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>informal communication style</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:044034</t>
+          <t>BCIO:044121</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>communication highlighting a contradiction</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>theatrical communication style</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:044022</t>
+          <t>BCIO:044000</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>communication adding intensity to another's views</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>behaviour change intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style that is an attribute of a BCI content communication process.</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>"overshooting" in motivational interviewing</t>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:044048</t>
+          <t>BCIO:044091</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>communication using deliberate pauses</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>communication style conveying hopefulness</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>staying silent (where this is intended to give others the chance to speak)</t>
+          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>optimism, positivity</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:044027</t>
+          <t>BCIO:044087</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>communication checking for own understanding</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>communication style conveying acceptance</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>clarifying what another has said</t>
-        </is>
-      </c>
       <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:044026</t>
+          <t>BCIO:044098</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>communication checking for others' understanding</t>
-        </is>
-      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>didactic communication style</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>gave a short lecture, conference presentation</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:044062</t>
+          <t>BCIO:050381</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>communication avoiding interrupting</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>angry communication style</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by anger.</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:044050</t>
+          <t>BCIO:044005</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>communication using particular language</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>A communication using certain vocabulary or phraseology.</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style that is an attribute of an intervention content communication process.</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:044056</t>
+          <t>BCIO:044111</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1569,32 +1628,32 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>communication using selected words from a second language</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>non-confrontational communication style</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:044054</t>
+          <t>BCIO:044113</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1602,36 +1661,36 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>communication using specialist language</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>patient communication style</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>using jargon</t>
+          <t>"willing to listen"</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:044055</t>
+          <t>BCIO:044114</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1639,32 +1698,32 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>communication avoiding offensive language</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>persuasive communication style</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:044053</t>
+          <t>BCIO:050380</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1672,32 +1731,32 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>communication using slang</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>aggressive communication style</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A communication using informal language shared by members of a particular community.</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by aggression.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:044052</t>
+          <t>BCIO:044107</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1705,32 +1764,32 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>communication using non-pressurising language</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>intellectual communication style</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:044051</t>
+          <t>BCIO:044095</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1738,181 +1797,182 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>communication using neutral language</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>communication style demonstrating positive regard</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:044060</t>
+          <t>BCIO:044117</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>guiding communication</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>respectful communication style</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>"acknowledging the victim's feelings"</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:044009</t>
+          <t>BCIO:044092</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>active listening</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>communication style conveying perceived superiority</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:044035</t>
+          <t>BCIO:044100</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>communication inviting reactions to content presented</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>easily comprehended communication style</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A communication seeking information about a person's responses to the  content presented.</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
         </is>
       </c>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>This can involve using plain and simple language</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>asking for opinions</t>
+          <t>using non-technical language, using clear language, avoiding jargon</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:044030</t>
+          <t>BCIO:044105</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>exploring communication</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>impatient communication style</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
         </is>
       </c>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>eliciting or seeking information</t>
-        </is>
-      </c>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:050383</t>
+          <t>BCIO:044123</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1920,36 +1980,36 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about a topic</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>warm communication style</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to a matter.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Elicit concerns, problems and reactions</t>
+          <t>A communication style which demonstrates human interest and caring.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>friendly communication style</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:050386</t>
+          <t>BCIO:044096</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1957,36 +2017,32 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about a topic</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>controlling communication style</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about a matter.</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>clarifying what someone has said</t>
-        </is>
-      </c>
       <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:050387</t>
+          <t>BCIO:044090</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1994,37 +2050,36 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about an experience</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>communication style conveying genuineness</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about an experience.</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>sincerity</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:050385</t>
+          <t>BCIO:044122</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2032,112 +2087,107 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about an experience</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>verbally dominant communication style</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to an experience.</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:044069</t>
+          <t>BCIO:050392</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>offering reassurance</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>rushed communication style</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style conveying information in a hurried way.</t>
         </is>
       </c>
       <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>made reassuring statements</t>
-        </is>
-      </c>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>based on Roter Interactional Analysis System</t>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:050388</t>
+          <t>BCIO:044109</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>communication showing acknowledgement</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>legitimising communication style</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A communication involving the expressed recognition of what another has expressed.</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>validating emotions</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
+        </is>
+      </c>
       <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:044021</t>
+          <t>BCIO:044119</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2145,145 +2195,143 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>communication acknowledging difficulties</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>semi-structured communication style</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>organised communication style</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:044042</t>
+          <t>BCIO:044102</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>communication understating intensity of person's views</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>engaging communication style</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>"undershooting" in motivational interviewing</t>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:044017</t>
+          <t>BCIO:044115</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>banter</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>polite communication style</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by courtesy.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:044001</t>
+          <t>BCIO:044082</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>intervention content communication process</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>articulate communication style</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A communication that transmits the content of an intervention</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>fluent</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:044002</t>
+          <t>BCIO:044120</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2291,141 +2339,149 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>behaviour change intervention content communication process</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>structured communication style</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>An intervention content communication process that is about behaviour change intervention content</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>standardised</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
+        </is>
+      </c>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:044070</t>
+          <t>BCIO:044083</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>paraphrasing</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>attentive communication style</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A communication in which one participant summarises what the other said.</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by purposeful consideration of another's statements.</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>"listened carefully to what you had to say"</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:044058</t>
+          <t>BCIO:044131</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>communication using rational arguments</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>anxious communication style</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by nervousness or unease.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:044071</t>
+          <t>BCIO:044094</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>reflective communication</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>communication style conveying support for change</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style which imparts one's belief that the recipient can change.</t>
         </is>
       </c>
       <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:044075</t>
+          <t>BCIO:044085</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2433,36 +2489,32 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>emotion-emphasising reflective communication</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>collaborative communication style</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
         </is>
       </c>
       <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>"reflection of feeling" in Motivational Interviewing</t>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:044074</t>
+          <t>BCIO:044104</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2470,36 +2522,32 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>metaphor-using reflective communication</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>formal communication style</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
         </is>
       </c>
       <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>"metaphorical reflection" in Motivational Interviewing</t>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:044073</t>
+          <t>BCIO:044081</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2507,36 +2555,32 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>double-sided reflective communication</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>aloof communication style</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
         </is>
       </c>
       <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>"double-sided reflection" in Motivational Interviewing</t>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:044076</t>
+          <t>BCIO:044127</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2544,36 +2588,36 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>re-evaluation prompting reflective communication</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>object visual style</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
         </is>
       </c>
       <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>"amplified reflection" in Motivational Interviewing</t>
+          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:044072</t>
+          <t>BCIO:044130</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2581,210 +2625,203 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>summarising reflective communication</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>readability</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
         </is>
       </c>
       <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>"summarising reflection" in Motivational Interviewing</t>
+          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:044029</t>
+          <t>BCIO:044125</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>communication evoking another's ideas about change</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>tone of voice</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>evoking change talk in motivational interviewing</t>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:044077</t>
+          <t>BCIO:044128</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>script-based communication</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>source visual style</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An attribute of an intervention person source concerning how they appear to others.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>may be purposefully chosen to convey certain attributes of the source</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:044012</t>
+          <t>BCIO:044129</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>asking questions</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>object layout</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>A communication in which some participant requests information from another participant.</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:050382</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>asking clarifying questions</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Asking questions in order to better understand an issue.</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:044016</t>
+          <t>BCIO:036000</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>asking open-ended questions</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>individual human behaviour</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
+          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:044014</t>
+          <t>BCIO:050457</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2794,7 +2831,7 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>asking focused questions</t>
+          <t>expressive behaviour</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -2802,22 +2839,22 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An individual human behaviour that conveys a thought or feeling.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:044013</t>
+          <t>BCIO:036034</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2825,32 +2862,32 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>asking closed-ended questions</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>human communication behaviour</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Asking questions that can only be answered with a limited set of responses.</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:044015</t>
+          <t>BCIO:050237</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2858,181 +2895,148 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>asking leading questions</t>
-        </is>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>linguistic communication behaviour</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>asking directive questions</t>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:044124</t>
+          <t>BCIO:050374</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>relationship building</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>laughing</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
-        </is>
-      </c>
       <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:044028</t>
+          <t>BCIO:050441</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>communication encouraging discussion</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>socially-related behaviour</t>
+        </is>
+      </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Contrasts with a more one-way, didactic style</t>
+          <t>An individual human behaviour that relates to the social environment.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:044039</t>
+          <t>BCIO:036025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>communication involving confirmatory rephrasing</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>inter-personal behaviour</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>"coming alongside" in Motivational Interviewing</t>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:044024</t>
+          <t>OBI:0000011</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>communication avoiding argumentation</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>planned process</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
+          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:044047</t>
+          <t>BCIO:045000</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3041,7 +3045,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>communication using commands</t>
+          <t>intervention delivery</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -3050,461 +3054,496 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A planned process by which intervention content is delivered.</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>communication using imperatives</t>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:044041</t>
+          <t>BCIO:044008</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>communication offering choice</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>source-led intervention delivery</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>A communication involving the initiator offering a range of options to the recipient.</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:044018</t>
+          <t>BCIO:044007</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>branded communication</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>participant-led intervention delivery</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>Change for Life, Time to Change, NHS Smokefree</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>use of branding; brand identity</t>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:044064</t>
+          <t>BCIO:008000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>narrative communication</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>behaviour change intervention delivery</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:044043</t>
+          <t>BCIO:044006</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>communication using a particular form of address</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>person-centred intervention delivery</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:044046</t>
+          <t>BCIO:050384</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>communication using preferred form of address</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A process involving the transmission of information between two or more participants.</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
+          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
         </is>
       </c>
       <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:044044</t>
+          <t>BCIO:044048</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>communication using formal address</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>communication using deliberate pauses</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>staying silent (where this is intended to give others the chance to speak)</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:044045</t>
+          <t>BCIO:044030</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>communication using informal address</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>exploring communication</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>eliciting or seeking information</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:044049</t>
+          <t>BCIO:050383</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>communication using interjections to signal attentiveness</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about a topic</t>
+        </is>
+      </c>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An exploring communication focused on a person's affective responses to a matter.</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>Words like "interesting", "yeah"," mmhmm"</t>
-        </is>
-      </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
+          <t>Elicit concerns, problems and reactions</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:044059</t>
+          <t>BCIO:050385</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>emotionally expressive communication</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about an experience</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An exploring communication focused on a person's affective responses to an experience.</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>BCIO:050386</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about a topic</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organsim participates.</t>
+          <t>An exploring communication focused on what a person thinks about a matter.</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>clarifying what someone has said</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:036000</t>
+          <t>BCIO:050387</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>individual human behaviour</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about an experience</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
+          <t>An exploring communication focused on what a person thinks about an experience.</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:050441</t>
+          <t>BCIO:044010</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>socially-related behaviour</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>affirming communication</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to the social environment.</t>
+          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Making explicit statements of partnership or support; Shows approval;</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:036025</t>
+          <t>BCIO:044050</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>communication using particular language</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>inter-personal behaviour</t>
-        </is>
-      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication using certain vocabulary or phraseology.</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:036034</t>
+          <t>BCIO:044056</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3512,32 +3551,32 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>human communication behaviour</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>communication using selected words from a second language</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
         </is>
       </c>
       <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:050237</t>
+          <t>BCIO:044055</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3545,32 +3584,32 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>communication avoiding offensive language</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>linguistic communication behaviour</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:050457</t>
+          <t>BCIO:044053</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3580,7 +3619,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>expressive behaviour</t>
+          <t>communication using slang</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -3588,22 +3627,22 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>An individual human behaviour that conveys a thought or feeling.</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication using informal language shared by members of a particular community.</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:050374</t>
+          <t>BCIO:044051</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3611,454 +3650,462 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>laughing</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>communication using neutral language</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>BCIO:044054</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>process profile</t>
-        </is>
-      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>communication using specialist language</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
+          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>using jargon</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:044052</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>process attribute</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>communication using non-pressurising language</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
+          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:044003</t>
+          <t>BCIO:044029</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>communication process attribute</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>communication evoking another's ideas about change</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>An attribute of a communication process.</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>evoking change talk in motivational interviewing</t>
+        </is>
+      </c>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:044126</t>
+          <t>BCIO:044042</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>communication understating intensity of person's views</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>oral communication pace</t>
-        </is>
-      </c>
+      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>"undershooting" in motivational interviewing</t>
+        </is>
+      </c>
       <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:044129</t>
+          <t>BCIO:044124</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>relationship building</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>object layout</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:044004</t>
+          <t>BCIO:044028</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>communication encouraging discussion</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>communication style</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Contrasts with a more one-way, didactic style</t>
+        </is>
+      </c>
       <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:044085</t>
+          <t>BCIO:044024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>communication avoiding argumentation</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>collaborative communication style</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:044000</t>
+          <t>BCIO:044018</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>branded communication</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>behaviour change intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of a BCI content communication process.</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
+          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>use of branding; brand identity</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Change for Life, Time to Change, NHS Smokefree</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:044099</t>
+          <t>BCIO:044058</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>communication using rational arguments</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>directive communication style</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>A communication style intended to play an active role in another person's decision making.</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
-        </is>
-      </c>
       <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>Note that this class is different from direct communication style</t>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:044117</t>
+          <t>BCIO:044070</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>paraphrasing</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>respectful communication style</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which one participant summarises what the other said.</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>"acknowledging the victim's feelings"</t>
+          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
         </is>
       </c>
       <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:044097</t>
+          <t>BCIO:044078</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>shifting focus of communication</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>conversational communication style</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:044106</t>
+          <t>BCIO:044012</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>asking questions</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>informal communication style</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which some participant requests information from another participant.</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:044109</t>
+          <t>BCIO:044016</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4066,41 +4113,32 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>asking open-ended questions</t>
+        </is>
+      </c>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>legitimising communication style</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>validating emotions</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:050381</t>
+          <t>BCIO:044013</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4108,32 +4146,32 @@
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>asking closed-ended questions</t>
+        </is>
+      </c>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>angry communication style</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>A communication style characterised by anger.</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>Asking questions that can only be answered with a limited set of responses.</t>
         </is>
       </c>
       <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:050380</t>
+          <t>BCIO:050382</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4141,32 +4179,32 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>asking clarifying questions</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>aggressive communication style</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>A communication style characterised by aggression.</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>Asking questions in order to better understand an issue.</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:044114</t>
+          <t>BCIO:044015</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4174,32 +4212,36 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>asking leading questions</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>persuasive communication style</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>asking directive questions</t>
+        </is>
+      </c>
       <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:044103</t>
+          <t>BCIO:044014</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4207,364 +4249,351 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>asking focused questions</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>entertaining communication style</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>fun</t>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:044083</t>
+          <t>BCIO:044059</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>emotionally expressive communication</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>attentive communication style</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>A communication style characterised by purposeful consideration of another's statements.</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>"listened carefully to what you had to say"</t>
-        </is>
-      </c>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:044102</t>
+          <t>BCIO:044026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>communication checking for others' understanding</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>engaging communication style</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:044104</t>
+          <t>BCIO:044040</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>communication involving elaboration of arguments</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>formal communication style</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:044082</t>
+          <t>BCIO:044041</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>communication offering choice</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>articulate communication style</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication involving the initiator offering a range of options to the recipient.</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>fluent</t>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:044118</t>
+          <t>BCIO:044049</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>communication using interjections to signal attentiveness</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>responsive communication style</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
+          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Words like "interesting", "yeah"," mmhmm"</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:044120</t>
+          <t>BCIO:044047</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>communication using commands</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>structured communication style</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>standardised</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
+          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>communication using imperatives</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:050392</t>
+          <t>BCIO:044065</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>negotiation</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>rushed communication style</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>A communication style conveying information in a hurried way.</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:044112</t>
+          <t>BCIO:044077</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>script-based communication</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>non-judgmental communication style</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
+        </is>
+      </c>
       <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:044091</t>
+          <t>BCIO:050388</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>communication showing acknowledgement</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>communication style conveying hopefulness</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication involving the expressed recognition of what another has expressed.</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>optimism, positivity</t>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:044084</t>
+          <t>BCIO:044021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4572,78 +4601,65 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>communication acknowledging difficulties</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>autonomy-supportive communication style</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>needs-supportive communication style</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>from Self-Determination Theory interventions.</t>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:044123</t>
+          <t>BCIO:044071</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>reflective communication</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>warm communication style</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>A communication style which demonstrates human interest and caring.</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>friendly communication style</t>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:044096</t>
+          <t>BCIO:044073</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4651,32 +4667,36 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>double-sided reflective communication</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>controlling communication style</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>"double-sided reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:044113</t>
+          <t>BCIO:044074</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4684,36 +4704,36 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>metaphor-using reflective communication</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>patient communication style</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>"willing to listen"</t>
+          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>"metaphorical reflection" in Motivational Interviewing</t>
         </is>
       </c>
       <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:050390</t>
+          <t>BCIO:044072</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4721,32 +4741,36 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>summarising reflective communication</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>humorous communication style</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>A communication style intended to amuse.</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>"summarising reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:044005</t>
+          <t>BCIO:044075</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4754,37 +4778,36 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>emotion-emphasising reflective communication</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of an intervention content communication process.</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>"reflection of feeling" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:044131</t>
+          <t>BCIO:044076</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4792,144 +4815,143 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>re-evaluation prompting reflective communication</t>
+        </is>
+      </c>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>anxious communication style</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>A communication style characterised by nervousness or unease.</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>"amplified reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:044090</t>
+          <t>BCIO:044039</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>communication involving confirmatory rephrasing</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>communication style conveying genuineness</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>sincerity</t>
+          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>"coming alongside" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:050389</t>
+          <t>BCIO:044035</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>communication inviting reactions to content presented</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>direct communication style</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>A communication style characterised by the explicit presentation of information.</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+          <t>A communication seeking information about a person's responses to the  content presented.</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>asking for opinions</t>
+        </is>
+      </c>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>Note that this class is different from directive communication style</t>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:044108</t>
+          <t>BCIO:044037</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>communication involving agreement</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>interactive communication style</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>A communication style characterised by being responsive to the recipient's activity.</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which one participant concurs with the views stated by another.</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>interactive presentation</t>
-        </is>
-      </c>
       <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:050391</t>
+          <t>BCIO:044038</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -4937,168 +4959,181 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>communication involving agreement followed by highlighting incongruent aspects</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>non-responsive communication style</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>"agreement with a twist" in motivational interviewing</t>
+        </is>
+      </c>
       <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:044095</t>
+          <t>BCIO:044060</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>guiding communication</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>communication style demonstrating positive regard</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:044115</t>
+          <t>BCIO:044061</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>interrupting</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>polite communication style</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>A communication style characterised by courtesy.</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which one person interjects before another has finished making their point.</t>
         </is>
       </c>
       <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:044116</t>
+          <t>BCIO:044011</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>agenda-sharing communication</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>relaxed communication style</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of tension or anxiety.</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>calm communication style</t>
+          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>agenda mapping</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:044107</t>
+          <t>BCIO:044019</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>discussion</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>intellectual communication style</t>
-        </is>
-      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
+        </is>
+      </c>
       <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:044098</t>
+          <t>BCIO:044020</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5106,407 +5141,436 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>classroom-style discussion</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>didactic communication style</t>
-        </is>
-      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>gave a short lecture, conference presentation</t>
-        </is>
-      </c>
       <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:044092</t>
+          <t>BCIO:044062</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>communication avoiding interrupting</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>communication style conveying perceived superiority</t>
-        </is>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:044122</t>
+          <t>BCIO:044069</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>offering reassurance</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>verbally dominant communication style</t>
-        </is>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
         </is>
       </c>
       <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>based on Roter Interactional Analysis System</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>made reassuring statements</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:044105</t>
+          <t>BCIO:044017</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>banter</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>impatient communication style</t>
-        </is>
-      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:044079</t>
+          <t>BCIO:044009</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>active listening</t>
+        </is>
+      </c>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>active participation encouraging communication style</t>
-        </is>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:044089</t>
+          <t>BCIO:044027</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>communication checking for own understanding</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>communication style conveying concern</t>
-        </is>
-      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>clarifying what another has said</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:044087</t>
+          <t>BCIO:044034</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>communication highlighting a contradiction</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>communication style conveying acceptance</t>
-        </is>
-      </c>
+      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
+        </is>
+      </c>
       <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:044111</t>
+          <t>BCIO:044023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>communication asking permission to provide information and advice</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>non-confrontational communication style</t>
-        </is>
-      </c>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
         </is>
       </c>
       <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BCIO:044119</t>
+          <t>BCIO:044022</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>communication adding intensity to another's views</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>semi-structured communication style</t>
-        </is>
-      </c>
+      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
-        </is>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>organised communication style</t>
+          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>"overshooting" in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:044081</t>
+          <t>BCIO:044064</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>narrative communication</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>aloof communication style</t>
-        </is>
-      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:044121</t>
+          <t>BCIO:044036</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>theatrical communication style</t>
-        </is>
-      </c>
+      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
         </is>
       </c>
       <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>From Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:044086</t>
+          <t>BCIO:044043</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>communication using a particular form of address</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>cold communication style</t>
-        </is>
-      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
         </is>
       </c>
       <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
+        </is>
+      </c>
       <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:044100</t>
+          <t>BCIO:044045</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5514,41 +5578,32 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>communication using informal address</t>
+        </is>
+      </c>
       <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>easily comprehended communication style</t>
-        </is>
-      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>using non-technical language, using clear language, avoiding jargon</t>
-        </is>
-      </c>
       <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>This can involve using plain and simple language</t>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:044110</t>
+          <t>BCIO:044044</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5556,32 +5611,32 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>communication using formal address</t>
+        </is>
+      </c>
       <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>non-defensive communication style</t>
-        </is>
-      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
         </is>
       </c>
       <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BCIO:044101</t>
+          <t>BCIO:044046</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5589,69 +5644,74 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>communication using preferred form of address</t>
+        </is>
+      </c>
       <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>empathic communication style</t>
-        </is>
-      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
-          <t>sensitivity, compassion</t>
+          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BCIO:044094</t>
+          <t>BCIO:044001</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>intervention content communication process</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr"/>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>communication style conveying support for change</t>
-        </is>
-      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>A communication style which imparts one's belief that the recipient can change.</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication that transmits the content of an intervention</t>
         </is>
       </c>
       <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
+        </is>
+      </c>
       <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BCIO:044130</t>
+          <t>BCIO:044002</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5659,272 +5719,220 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>readability</t>
-        </is>
-      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>behaviour change intervention content communication process</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An intervention content communication process that is about behaviour change intervention content</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
-          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
+          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
         </is>
       </c>
       <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BCIO:044125</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>continuant</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>tone of voice</t>
-        </is>
-      </c>
+      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
-        </is>
-      </c>
-      <c r="L153" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BCIO:044128</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>generically dependent continuant</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>source visual style</t>
-        </is>
-      </c>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>An attribute of an intervention person source concerning how they appear to others.</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>may be purposefully chosen to convey certain attributes of the source</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BCIO:044127</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>object visual style</t>
-        </is>
-      </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr"/>
+          <t>A generically dependent continuant that is about some thing.</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>BCIO:050555</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>communication message</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
+          <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BCIO:045000</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>intervention delivery</t>
-        </is>
-      </c>
+      <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>A planned process by which intervention content is delivered.</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
+          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BCIO:044007</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>participant-led intervention delivery</t>
-        </is>
-      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BCIO:044006</t>
+          <t>OGMS:0000087</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>person-centred intervention delivery</t>
-        </is>
-      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>extended organism</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
+          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BCIO:008000</t>
+          <t>MF:0000016</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
@@ -5934,7 +5942,7 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>behaviour change intervention delivery</t>
+          <t>human being</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
@@ -5942,22 +5950,14 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BCIO:044008</t>
+          <t>BCIO:050553</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -5965,60 +5965,60 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>source-led intervention delivery</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>communication recipient</t>
+        </is>
+      </c>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A &lt;person&gt; who receives a communication.</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:050552</t>
+          <t>BCIO:050554</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>communication channel</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>communication source</t>
+        </is>
+      </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; by which a communication is delivered.</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A &lt;material entity&gt; that originates a communication.</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/StyleOfDelivery/BCIO-style-hierarchy.xlsx
+++ b/StyleOfDelivery/BCIO-style-hierarchy.xlsx
@@ -442,32 +442,32 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>informaldefinition</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>comment</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>subontology</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIO:050552</t>
+          <t>OBI:0000011</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -582,7 +582,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>communication channel</t>
+          <t>planned process</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -592,72 +592,80 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; by which a communication is delivered.</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>BCIO:045000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>process profile</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>intervention delivery</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
-        </is>
-      </c>
+          <t>A planned process by which intervention content is delivered.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:044008</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>process attribute</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>source-led intervention delivery</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
-        </is>
-      </c>
+          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:044003</t>
+          <t>BCIO:008000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -667,7 +675,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>communication process attribute</t>
+          <t>behaviour change intervention delivery</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -675,27 +683,22 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>An attribute of a communication process.</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
-        </is>
-      </c>
+          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:044126</t>
+          <t>BCIO:044006</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -703,32 +706,32 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>oral communication pace</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>person-centred intervention delivery</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:044004</t>
+          <t>BCIO:044007</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -736,172 +739,174 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>communication style</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>participant-led intervention delivery</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050391</t>
+          <t>BCIO:050384</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>non-responsive communication style</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>A process involving the transmission of information between two or more participants.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:044108</t>
+          <t>BCIO:044064</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>narrative communication</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>interactive communication style</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A communication style characterised by being responsive to the recipient's activity.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>interactive presentation</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:044101</t>
+          <t>BCIO:044017</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>banter</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>empathic communication style</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
-        </is>
-      </c>
+          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>sensitivity, compassion</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:044089</t>
+          <t>BCIO:044071</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>reflective communication</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>communication style conveying concern</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:044086</t>
+          <t>BCIO:044073</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -909,32 +914,36 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>double-sided reflective communication</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>cold communication style</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>"double-sided reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:050389</t>
+          <t>BCIO:044072</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -942,37 +951,36 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>summarising reflective communication</t>
+        </is>
+      </c>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>direct communication style</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A communication style characterised by the explicit presentation of information.</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Note that this class is different from directive communication style</t>
-        </is>
-      </c>
+          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>"summarising reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:044097</t>
+          <t>BCIO:044075</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -980,32 +988,36 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>emotion-emphasising reflective communication</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>conversational communication style</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>"reflection of feeling" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:044103</t>
+          <t>BCIO:044074</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1013,36 +1025,36 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>metaphor-using reflective communication</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>entertaining communication style</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
+          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>"metaphorical reflection" in Motivational Interviewing</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>fun</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:044079</t>
+          <t>BCIO:044076</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1050,178 +1062,186 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>re-evaluation prompting reflective communication</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>active participation encouraging communication style</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
+          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>"amplified reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:050390</t>
+          <t>BCIO:044009</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>active listening</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>humorous communication style</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>A communication style intended to amuse.</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:044112</t>
+          <t>BCIO:044069</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>offering reassurance</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>non-judgmental communication style</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>made reassuring statements</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>based on Roter Interactional Analysis System</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:044099</t>
+          <t>BCIO:044011</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>agenda-sharing communication</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>directive communication style</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A communication style intended to play an active role in another person's decision making.</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>Note that this class is different from direct communication style</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>agenda mapping</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:044118</t>
+          <t>BCIO:044019</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>discussion</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>responsive communication style</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
-        </is>
-      </c>
+          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:044116</t>
+          <t>BCIO:044020</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1229,290 +1249,280 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>classroom-style discussion</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>relaxed communication style</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of tension or anxiety.</t>
-        </is>
-      </c>
+          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>calm communication style</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:044110</t>
+          <t>BCIO:044039</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>communication involving confirmatory rephrasing</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>non-defensive communication style</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>"coming alongside" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:044084</t>
+          <t>BCIO:044077</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>script-based communication</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>autonomy-supportive communication style</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
-        </is>
-      </c>
+          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>needs-supportive communication style</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>from Self-Determination Theory interventions.</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:044106</t>
+          <t>BCIO:044035</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>communication inviting reactions to content presented</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>informal communication style</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
-        </is>
-      </c>
+          <t>A communication seeking information about a person's responses to the  content presented.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>asking for opinions</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:044121</t>
+          <t>BCIO:044065</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>negotiation</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>theatrical communication style</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
+          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:044000</t>
+          <t>BCIO:044040</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>communication involving elaboration of arguments</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>behaviour change intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of a BCI content communication process.</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
-        </is>
-      </c>
+          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:044091</t>
+          <t>BCIO:044060</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>guiding communication</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>communication style conveying hopefulness</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
-        </is>
-      </c>
+          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>optimism, positivity</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:044087</t>
+          <t>BCIO:044037</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>communication involving agreement</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>communication style conveying acceptance</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>A communication in which one participant concurs with the views stated by another.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:044098</t>
+          <t>BCIO:044038</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1520,140 +1530,143 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>communication involving agreement followed by highlighting incongruent aspects</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>didactic communication style</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>gave a short lecture, conference presentation</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>"agreement with a twist" in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:050381</t>
+          <t>BCIO:044022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>communication adding intensity to another's views</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>angry communication style</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A communication style characterised by anger.</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>"overshooting" in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:044005</t>
+          <t>BCIO:044029</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>communication evoking another's ideas about change</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of an intervention content communication process.</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
-        </is>
-      </c>
+          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>evoking change talk in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:044111</t>
+          <t>BCIO:044050</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>communication using particular language</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>non-confrontational communication style</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
+          <t>A communication using certain vocabulary or phraseology.</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:044113</t>
+          <t>BCIO:044055</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1661,36 +1674,32 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>communication avoiding offensive language</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>patient communication style</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>"willing to listen"</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:044114</t>
+          <t>BCIO:044051</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1698,32 +1707,32 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>communication using neutral language</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>persuasive communication style</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:050380</t>
+          <t>BCIO:044056</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1731,32 +1740,32 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>communication using selected words from a second language</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>aggressive communication style</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A communication style characterised by aggression.</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
+          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:044107</t>
+          <t>BCIO:044054</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1764,32 +1773,36 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>communication using specialist language</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>intellectual communication style</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>using jargon</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:044095</t>
+          <t>BCIO:044052</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1797,32 +1810,32 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>communication using non-pressurising language</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>communication style demonstrating positive regard</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:044117</t>
+          <t>BCIO:044053</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1830,74 +1843,65 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>communication using slang</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>respectful communication style</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>"acknowledging the victim's feelings"</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication using informal language shared by members of a particular community.</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:044092</t>
+          <t>BCIO:044012</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>asking questions</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>communication style conveying perceived superiority</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
+          <t>A communication in which some participant requests information from another participant.</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:044100</t>
+          <t>BCIO:044014</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1905,41 +1909,32 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>asking focused questions</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>easily comprehended communication style</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>This can involve using plain and simple language</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>using non-technical language, using clear language, avoiding jargon</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:044105</t>
+          <t>BCIO:050382</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1947,32 +1942,32 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>asking clarifying questions</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>impatient communication style</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>Asking questions in order to better understand an issue.</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:044123</t>
+          <t>BCIO:044016</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1980,36 +1975,32 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>asking open-ended questions</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>warm communication style</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>A communication style which demonstrates human interest and caring.</t>
-        </is>
-      </c>
+          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>friendly communication style</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:044096</t>
+          <t>BCIO:044015</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2017,32 +2008,36 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>asking leading questions</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>controlling communication style</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>asking directive questions</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:044090</t>
+          <t>BCIO:044013</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2050,185 +2045,177 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>asking closed-ended questions</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>communication style conveying genuineness</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
-        </is>
-      </c>
+          <t>Asking questions that can only be answered with a limited set of responses.</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>sincerity</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:044122</t>
+          <t>BCIO:044010</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>affirming communication</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>verbally dominant communication style</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Making explicit statements of partnership or support; Shows approval;</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:050392</t>
+          <t>BCIO:044048</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>communication using deliberate pauses</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>rushed communication style</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A communication style conveying information in a hurried way.</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
+          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>staying silent (where this is intended to give others the chance to speak)</t>
+        </is>
+      </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:044109</t>
+          <t>BCIO:044041</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>communication offering choice</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>legitimising communication style</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
-        </is>
-      </c>
+          <t>A communication involving the initiator offering a range of options to the recipient.</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>validating emotions</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:044119</t>
+          <t>BCIO:050388</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>communication showing acknowledgement</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>semi-structured communication style</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
-        </is>
-      </c>
+          <t>A communication involving the expressed recognition of what another has expressed.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>organised communication style</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:044102</t>
+          <t>BCIO:044021</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2236,252 +2223,244 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>communication acknowledging difficulties</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>engaging communication style</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:044115</t>
+          <t>BCIO:044047</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>communication using commands</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>polite communication style</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>A communication style characterised by courtesy.</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>communication using imperatives</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:044082</t>
+          <t>BCIO:044036</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>articulate communication style</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
-        </is>
-      </c>
+          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>fluent</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>From Motivational Interviewing</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:044120</t>
+          <t>BCIO:044059</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>emotionally expressive communication</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>structured communication style</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
-        </is>
-      </c>
+          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>standardised</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:044083</t>
+          <t>BCIO:044058</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>communication using rational arguments</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>attentive communication style</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A communication style characterised by purposeful consideration of another's statements.</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>"listened carefully to what you had to say"</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:044131</t>
+          <t>BCIO:044061</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>interrupting</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>anxious communication style</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>A communication style characterised by nervousness or unease.</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+          <t>A communication in which one person interjects before another has finished making their point.</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:044094</t>
+          <t>BCIO:044001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>intervention content communication process</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>communication style conveying support for change</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A communication style which imparts one's belief that the recipient can change.</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>A communication that transmits the content of an intervention</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:044085</t>
+          <t>BCIO:044002</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2489,339 +2468,378 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>behaviour change intervention content communication process</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>collaborative communication style</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>An intervention content communication process that is about behaviour change intervention content</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:044104</t>
+          <t>BCIO:044124</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>relationship building</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>formal communication style</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:044081</t>
+          <t>BCIO:044028</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>communication encouraging discussion</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>aloof communication style</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
+          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Contrasts with a more one-way, didactic style</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:044127</t>
+          <t>BCIO:044018</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>branded communication</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>object visual style</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
+          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>use of branding; brand identity</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>Change for Life, Time to Change, NHS Smokefree</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:044130</t>
+          <t>BCIO:044023</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>communication asking permission to provide information and advice</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>readability</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr">
         <is>
-          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:044125</t>
+          <t>BCIO:044062</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>communication avoiding interrupting</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>tone of voice</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
+          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:044128</t>
+          <t>BCIO:044034</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>communication highlighting a contradiction</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>source visual style</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>An attribute of an intervention person source concerning how they appear to others.</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>may be purposefully chosen to convey certain attributes of the source</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
+          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:044129</t>
+          <t>BCIO:044030</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>exploring communication</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>object layout</t>
-        </is>
-      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
-        </is>
-      </c>
+          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
+          <t>eliciting or seeking information</t>
+        </is>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>BCIO:050385</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about an experience</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organsim participates.</t>
+          <t>An exploring communication focused on a person's affective responses to an experience.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:036000</t>
+          <t>BCIO:050386</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>individual human behaviour</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about a topic</t>
+        </is>
+      </c>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
+          <t>An exploring communication focused on what a person thinks about a matter.</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>clarifying what someone has said</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:050457</t>
+          <t>BCIO:050383</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2831,7 +2849,7 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>expressive behaviour</t>
+          <t>communication exploring a person's feelings about a topic</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -2839,22 +2857,26 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>An individual human behaviour that conveys a thought or feeling.</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An exploring communication focused on a person's affective responses to a matter.</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Elicit concerns, problems and reactions</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:036034</t>
+          <t>BCIO:050387</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2862,98 +2884,108 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>human communication behaviour</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about an experience</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
+          <t>An exploring communication focused on what a person thinks about an experience.</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:050237</t>
+          <t>BCIO:044026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>communication checking for others' understanding</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>linguistic communication behaviour</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:050374</t>
+          <t>BCIO:044043</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>communication using a particular form of address</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>laughing</t>
-        </is>
-      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:050441</t>
+          <t>BCIO:044044</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2963,7 +2995,7 @@
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>socially-related behaviour</t>
+          <t>communication using formal address</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -2971,14 +3003,22 @@
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to the social environment.</t>
-        </is>
-      </c>
+          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:036025</t>
+          <t>BCIO:044045</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2986,57 +3026,69 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>inter-personal behaviour</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>communication using informal address</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>BCIO:044046</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>communication using preferred form of address</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
+          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:045000</t>
+          <t>BCIO:044078</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3045,7 +3097,7 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>intervention delivery</t>
+          <t>shifting focus of communication</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
@@ -3054,234 +3106,238 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>A planned process by which intervention content is delivered.</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr"/>
+          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:044008</t>
+          <t>BCIO:044042</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>source-led intervention delivery</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>communication understating intensity of person's views</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr"/>
+          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>"undershooting" in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:044007</t>
+          <t>BCIO:044070</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>participant-led intervention delivery</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>paraphrasing</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
+          <t>A communication in which one participant summarises what the other said.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:008000</t>
+          <t>BCIO:044049</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>behaviour change intervention delivery</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>communication using interjections to signal attentiveness</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Words like "interesting", "yeah"," mmhmm"</t>
+        </is>
+      </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:044006</t>
+          <t>BCIO:044027</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>person-centred intervention delivery</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>communication checking for own understanding</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>clarifying what another has said</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:050384</t>
+          <t>BCIO:044024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>communication avoiding argumentation</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>A process involving the transmission of information between two or more participants.</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
-        </is>
-      </c>
+          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:044048</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>communication using deliberate pauses</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>staying silent (where this is intended to give others the chance to speak)</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:044030</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3290,7 +3346,7 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>exploring communication</t>
+          <t>process attribute</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3299,31 +3355,14 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>eliciting or seeking information</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A process profile that is an attribute of a process.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:050383</t>
+          <t>BCIO:044003</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
@@ -3333,7 +3372,7 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>communication exploring a person's feelings about a topic</t>
+          <t>communication process attribute</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -3341,26 +3380,27 @@
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to a matter.</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>Elicit concerns, problems and reactions</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr"/>
+          <t>An attribute of a communication process.</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:050385</t>
+          <t>BCIO:044129</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3368,37 +3408,41 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about an experience</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>object layout</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to an experience.</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
+          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
+        </is>
+      </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:050386</t>
+          <t>BCIO:044004</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -3406,36 +3450,32 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about a topic</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>communication style</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about a matter.</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>clarifying what someone has said</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:050387</t>
+          <t>BCIO:044107</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3443,107 +3483,107 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about an experience</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>intellectual communication style</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about an experience.</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
-        </is>
-      </c>
+          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:044010</t>
+          <t>BCIO:044094</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>affirming communication</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>communication style conveying support for change</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Making explicit statements of partnership or support; Shows approval;</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style which imparts one's belief that the recipient can change.</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:044050</t>
+          <t>BCIO:044100</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>communication using particular language</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>easily comprehended communication style</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>A communication using certain vocabulary or phraseology.</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
+          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>using non-technical language, using clear language, avoiding jargon</t>
+        </is>
+      </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This can involve using plain and simple language</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:044056</t>
+          <t>BCIO:044116</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3551,32 +3591,36 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>communication using selected words from a second language</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>relaxed communication style</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr"/>
+          <t>A communication style characterised by a lack of tension or anxiety.</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>calm communication style</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:044055</t>
+          <t>BCIO:044110</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -3584,32 +3628,32 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>communication avoiding offensive language</t>
-        </is>
-      </c>
+      <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>non-defensive communication style</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
+          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:044053</t>
+          <t>BCIO:044099</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -3617,32 +3661,41 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>communication using slang</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>directive communication style</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>A communication using informal language shared by members of a particular community.</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
+          <t>A communication style intended to play an active role in another person's decision making.</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
+        </is>
+      </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Note that this class is different from direct communication style</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:044051</t>
+          <t>BCIO:044005</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
@@ -3650,32 +3703,37 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>communication using neutral language</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr"/>
+          <t>A communication style that is an attribute of an intervention content communication process.</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:044054</t>
+          <t>BCIO:044106</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -3683,36 +3741,37 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>communication using specialist language</t>
-        </is>
-      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>informal communication style</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
-        </is>
-      </c>
+          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>using jargon</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:044052</t>
+          <t>BCIO:044119</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3720,392 +3779,397 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>communication using non-pressurising language</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>semi-structured communication style</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>organised communication style</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:044029</t>
+          <t>BCIO:044091</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>communication evoking another's ideas about change</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>communication style conveying hopefulness</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
+          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>optimism, positivity</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>evoking change talk in motivational interviewing</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:044042</t>
+          <t>BCIO:044118</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>communication understating intensity of person's views</t>
-        </is>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>responsive communication style</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
-        </is>
-      </c>
+          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>"undershooting" in motivational interviewing</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:044124</t>
+          <t>BCIO:044087</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>relationship building</t>
-        </is>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>communication style conveying acceptance</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr"/>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:044028</t>
+          <t>BCIO:044089</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>communication encouraging discussion</t>
-        </is>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>communication style conveying concern</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>Contrasts with a more one-way, didactic style</t>
-        </is>
-      </c>
+          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:044024</t>
+          <t>BCIO:044115</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>communication avoiding argumentation</t>
-        </is>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>polite communication style</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr"/>
+          <t>A communication style characterised by courtesy.</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:044018</t>
+          <t>BCIO:044109</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>branded communication</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>legitimising communication style</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
+          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>validating emotions</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>use of branding; brand identity</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>Change for Life, Time to Change, NHS Smokefree</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr"/>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:044058</t>
+          <t>BCIO:044081</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>communication using rational arguments</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>aloof communication style</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr"/>
+          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:044070</t>
+          <t>BCIO:044092</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>paraphrasing</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>communication style conveying perceived superiority</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>A communication in which one participant summarises what the other said.</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
-        </is>
-      </c>
+          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:044078</t>
+          <t>BCIO:044084</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>shifting focus of communication</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>autonomy-supportive communication style</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr"/>
+          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>needs-supportive communication style</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>from Self-Determination Theory interventions.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:044012</t>
+          <t>BCIO:044112</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>asking questions</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>non-judgmental communication style</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>A communication in which some participant requests information from another participant.</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr"/>
+          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:044016</t>
+          <t>BCIO:044000</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -4113,32 +4177,37 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>asking open-ended questions</t>
-        </is>
-      </c>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>behaviour change intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr"/>
+          <t>A communication style that is an attribute of a BCI content communication process.</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:044013</t>
+          <t>BCIO:044108</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -4146,32 +4215,36 @@
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>asking closed-ended questions</t>
-        </is>
-      </c>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>interactive communication style</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Asking questions that can only be answered with a limited set of responses.</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by being responsive to the recipient's activity.</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>interactive presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:050382</t>
+          <t>BCIO:044104</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4179,32 +4252,32 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>asking clarifying questions</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>formal communication style</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Asking questions in order to better understand an issue.</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr"/>
+          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:044015</t>
+          <t>BCIO:044097</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4212,36 +4285,32 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>asking leading questions</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>conversational communication style</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
-        </is>
-      </c>
+          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>asking directive questions</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:044014</t>
+          <t>BCIO:044085</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4249,351 +4318,351 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>asking focused questions</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>collaborative communication style</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr"/>
+          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:044059</t>
+          <t>BCIO:044105</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>emotionally expressive communication</t>
-        </is>
-      </c>
+      <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>impatient communication style</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr"/>
+          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:044026</t>
+          <t>BCIO:044123</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>communication checking for others' understanding</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>warm communication style</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr"/>
+          <t>A communication style which demonstrates human interest and caring.</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>friendly communication style</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:044040</t>
+          <t>BCIO:050390</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>communication involving elaboration of arguments</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>humorous communication style</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr"/>
+          <t>A communication style intended to amuse.</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:044041</t>
+          <t>BCIO:044111</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>communication offering choice</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>non-confrontational communication style</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>A communication involving the initiator offering a range of options to the recipient.</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr"/>
+          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:044049</t>
+          <t>BCIO:044101</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>communication using interjections to signal attentiveness</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>empathic communication style</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
+          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>sensitivity, compassion</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>Words like "interesting", "yeah"," mmhmm"</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:044047</t>
+          <t>BCIO:050389</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>communication using commands</t>
-        </is>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>direct communication style</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
-        </is>
-      </c>
+          <t>A communication style characterised by the explicit presentation of information.</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>communication using imperatives</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>Note that this class is different from directive communication style</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:044065</t>
+          <t>BCIO:044083</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>negotiation</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>attentive communication style</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
+          <t>A communication style characterised by purposeful consideration of another's statements.</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>"listened carefully to what you had to say"</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:044077</t>
+          <t>BCIO:044079</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>script-based communication</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>active participation encouraging communication style</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
-        </is>
-      </c>
+          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:050388</t>
+          <t>BCIO:050392</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>communication showing acknowledgement</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>rushed communication style</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>A communication involving the expressed recognition of what another has expressed.</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr"/>
+          <t>A communication style conveying information in a hurried way.</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:044021</t>
+          <t>BCIO:044113</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4601,65 +4670,73 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>communication acknowledging difficulties</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>patient communication style</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>"willing to listen"</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:044071</t>
+          <t>BCIO:044103</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>reflective communication</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>entertaining communication style</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr"/>
+          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:044073</t>
+          <t>BCIO:044122</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4667,36 +4744,32 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>double-sided reflective communication</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>verbally dominant communication style</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
-        </is>
-      </c>
+          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr"/>
       <c r="M123" t="inlineStr">
         <is>
-          <t>"double-sided reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:044074</t>
+          <t>BCIO:050391</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4704,36 +4777,32 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>metaphor-using reflective communication</t>
-        </is>
-      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>non-responsive communication style</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
-        </is>
-      </c>
+          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>"metaphorical reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:044072</t>
+          <t>BCIO:044090</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4741,36 +4810,36 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>summarising reflective communication</t>
-        </is>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>communication style conveying genuineness</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
+          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>sincerity</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>"summarising reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:044075</t>
+          <t>BCIO:050380</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4778,36 +4847,32 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>emotion-emphasising reflective communication</t>
-        </is>
-      </c>
+      <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>aggressive communication style</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
-        </is>
-      </c>
+          <t>A communication style characterised by aggression.</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>"reflection of feeling" in Motivational Interviewing</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:044076</t>
+          <t>BCIO:044086</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4815,143 +4880,140 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>re-evaluation prompting reflective communication</t>
-        </is>
-      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>cold communication style</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
-        </is>
-      </c>
+          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
-          <t>"amplified reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:044039</t>
+          <t>BCIO:044121</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>communication involving confirmatory rephrasing</t>
-        </is>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>theatrical communication style</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
-        </is>
-      </c>
+          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>"coming alongside" in Motivational Interviewing</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:044035</t>
+          <t>BCIO:044095</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>communication inviting reactions to content presented</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>communication style demonstrating positive regard</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>A communication seeking information about a person's responses to the  content presented.</t>
-        </is>
-      </c>
+          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
-          <t>asking for opinions</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:044037</t>
+          <t>BCIO:044120</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>communication involving agreement</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>structured communication style</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>A communication in which one participant concurs with the views stated by another.</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr"/>
+          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>standardised</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:044038</t>
+          <t>BCIO:044082</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -4959,181 +5021,172 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>communication involving agreement followed by highlighting incongruent aspects</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>articulate communication style</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
+          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>fluent</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>"agreement with a twist" in motivational interviewing</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:044060</t>
+          <t>BCIO:050381</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>guiding communication</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>angry communication style</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by anger.</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:044061</t>
+          <t>BCIO:044098</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>interrupting</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>didactic communication style</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>A communication in which one person interjects before another has finished making their point.</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>gave a short lecture, conference presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:044011</t>
+          <t>BCIO:044131</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>agenda-sharing communication</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>anxious communication style</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
-        </is>
-      </c>
+          <t>A communication style characterised by nervousness or unease.</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>agenda mapping</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:044019</t>
+          <t>BCIO:044114</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>discussion</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>persuasive communication style</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
-        </is>
-      </c>
+          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:044020</t>
+          <t>BCIO:044117</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5141,327 +5194,314 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>classroom-style discussion</t>
-        </is>
-      </c>
+      <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>respectful communication style</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
+          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>"acknowledging the victim's feelings"</t>
+        </is>
+      </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:044062</t>
+          <t>BCIO:044096</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>communication avoiding interrupting</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>controlling communication style</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr"/>
+          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:044069</t>
+          <t>BCIO:044102</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>offering reassurance</t>
-        </is>
-      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>engaging communication style</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>based on Roter Interactional Analysis System</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>made reassuring statements</t>
-        </is>
-      </c>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:044017</t>
+          <t>BCIO:044128</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>banter</t>
-        </is>
-      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>source visual style</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
-        </is>
-      </c>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
+          <t>An attribute of an intervention person source concerning how they appear to others.</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
+        </is>
+      </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>style of delivery</t>
+          <t>may be purposefully chosen to convey certain attributes of the source</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:044009</t>
+          <t>BCIO:044127</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>active listening</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>object visual style</t>
+        </is>
+      </c>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
-        </is>
-      </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:044027</t>
+          <t>BCIO:044126</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>communication checking for own understanding</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>oral communication pace</t>
+        </is>
+      </c>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>clarifying what another has said</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:044034</t>
+          <t>BCIO:044130</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>communication highlighting a contradiction</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>readability</t>
+        </is>
+      </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:044023</t>
+          <t>BCIO:044125</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>communication asking permission to provide information and advice</t>
-        </is>
-      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>tone of voice</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr"/>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
-        </is>
-      </c>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BCIO:044022</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>communication adding intensity to another's views</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>"overshooting" in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A process in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:044064</t>
+          <t>BCIO:036000</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5470,7 +5510,7 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>narrative communication</t>
+          <t>individual human behaviour</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -5479,98 +5519,72 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
-        </is>
-      </c>
-      <c r="M145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:044036</t>
+          <t>BCIO:050441</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>socially-related behaviour</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
-        </is>
-      </c>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>From Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An individual human behaviour that relates to the social environment.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:044043</t>
+          <t>BCIO:036025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>communication using a particular form of address</t>
-        </is>
-      </c>
+      <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>inter-personal behaviour</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
-        </is>
-      </c>
+          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:044045</t>
+          <t>BCIO:036034</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5578,32 +5592,32 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>communication using informal address</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>human communication behaviour</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="M148" t="inlineStr"/>
+          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:044044</t>
+          <t>BCIO:050237</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5611,32 +5625,32 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>communication using formal address</t>
-        </is>
-      </c>
+      <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>linguistic communication behaviour</t>
+        </is>
+      </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr"/>
+          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BCIO:044046</t>
+          <t>BCIO:050457</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5646,7 +5660,7 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>communication using preferred form of address</t>
+          <t>expressive behaviour</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -5654,97 +5668,83 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr"/>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>An individual human behaviour that conveys a thought or feeling.</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BCIO:044001</t>
+          <t>BCIO:050374</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>intervention content communication process</t>
-        </is>
-      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>laughing</t>
+        </is>
+      </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>A communication that transmits the content of an intervention</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
-        </is>
-      </c>
+          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BCIO:044002</t>
+          <t>BCIO:050552</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>communication channel</t>
+        </is>
+      </c>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>behaviour change intervention content communication process</t>
-        </is>
-      </c>
+      <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>An intervention content communication process that is about behaviour change intervention content</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
-        </is>
-      </c>
+          <t>A &lt;process&gt; by which a communication is delivered.</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5774,14 +5774,14 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>generically dependent continuant</t>
+          <t>independent continuant</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -5792,14 +5792,14 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -5807,7 +5807,7 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -5817,14 +5817,14 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BCIO:050555</t>
+          <t>OGMS:0000087</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -5833,7 +5833,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>communication message</t>
+          <t>extended organism</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -5842,72 +5842,72 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>MF:0000016</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>independent continuant</t>
-        </is>
-      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>human being</t>
+        </is>
+      </c>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>BCIO:050553</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>communication recipient</t>
+        </is>
+      </c>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
-        </is>
-      </c>
+          <t>A &lt;person&gt; who receives a communication.</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OGMS:0000087</t>
+          <t>BCIO:050554</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -5916,7 +5916,7 @@
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>extended organism</t>
+          <t>communication source</t>
         </is>
       </c>
       <c r="G159" t="inlineStr"/>
@@ -5925,72 +5925,72 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
-        </is>
-      </c>
+          <t>A &lt;material entity&gt; that originates a communication.</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>generically dependent continuant</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>human being</t>
-        </is>
-      </c>
+      <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BCIO:050553</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>communication recipient</t>
-        </is>
-      </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; who receives a communication.</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+          <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:050554</t>
+          <t>BCIO:050555</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -5999,7 +5999,7 @@
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>communication source</t>
+          <t>communication message</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
@@ -6008,17 +6008,17 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>A &lt;material entity&gt; that originates a communication.</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr"/>
+          <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/StyleOfDelivery/BCIO-style-hierarchy.xlsx
+++ b/StyleOfDelivery/BCIO-style-hierarchy.xlsx
@@ -442,27 +442,27 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>crossreference</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>subontology</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>crossreference</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>examples</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -574,7 +574,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -582,7 +582,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>planned process</t>
+          <t>bodily process</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -592,14 +592,14 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
+          <t>A process in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:045000</t>
+          <t>BCIO:036000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -608,7 +608,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>intervention delivery</t>
+          <t>individual human behaviour</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -617,22 +617,14 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>A planned process by which intervention content is delivered.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:044008</t>
+          <t>BCIO:050457</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -642,7 +634,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>source-led intervention delivery</t>
+          <t>expressive behaviour</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -650,22 +642,22 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
+          <t>An individual human behaviour that conveys a thought or feeling.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:008000</t>
+          <t>BCIO:036034</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -673,32 +665,32 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>behaviour change intervention delivery</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>human communication behaviour</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
+          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:044006</t>
+          <t>BCIO:050237</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -706,32 +698,32 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>person-centred intervention delivery</t>
-        </is>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>linguistic communication behaviour</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
+          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:044007</t>
+          <t>BCIO:050374</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -739,141 +731,115 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>participant-led intervention delivery</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>laughing</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
+          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050384</t>
+          <t>BCIO:050441</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>socially-related behaviour</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>A process involving the transmission of information between two or more participants.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
+          <t>An individual human behaviour that relates to the social environment.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:044064</t>
+          <t>BCIO:036025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>narrative communication</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>inter-personal behaviour</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
+          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:044017</t>
+          <t>OBI:0000011</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>banter</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>planned process</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
+          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:044071</t>
+          <t>BCIO:045000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -882,7 +848,7 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>reflective communication</t>
+          <t>intervention delivery</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -891,22 +857,22 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
+          <t>A planned process by which intervention content is delivered.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:044073</t>
+          <t>BCIO:008000</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -916,7 +882,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>double-sided reflective communication</t>
+          <t>behaviour change intervention delivery</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -924,26 +890,22 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>"double-sided reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:044072</t>
+          <t>BCIO:044007</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -953,7 +915,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>summarising reflective communication</t>
+          <t>participant-led intervention delivery</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -961,26 +923,22 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>"summarising reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:044075</t>
+          <t>BCIO:044008</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -990,7 +948,7 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>emotion-emphasising reflective communication</t>
+          <t>source-led intervention delivery</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -998,26 +956,22 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>"reflection of feeling" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:044074</t>
+          <t>BCIO:044006</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1027,7 +981,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>metaphor-using reflective communication</t>
+          <t>person-centred intervention delivery</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1035,96 +989,80 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>"metaphorical reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:044076</t>
+          <t>BCIO:050552</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>communication channel</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>re-evaluation prompting reflective communication</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>"amplified reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+          <t>A &lt;process&gt; by which a communication is delivered.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:044009</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>active listening</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:044069</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1133,7 +1071,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>offering reassurance</t>
+          <t>process attribute</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1142,106 +1080,89 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>made reassuring statements</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>based on Roter Interactional Analysis System</t>
+          <t>A process profile that is an attribute of a process.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:044011</t>
+          <t>BCIO:044003</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>agenda-sharing communication</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>communication process attribute</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>agenda mapping</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+          <t>An attribute of a communication process.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:044019</t>
+          <t>BCIO:044130</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>discussion</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>readability</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
+          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
+      <c r="M24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:044020</t>
+          <t>BCIO:044129</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1249,280 +1170,289 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>classroom-style discussion</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>object layout</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
+          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:044039</t>
+          <t>BCIO:044126</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>communication involving confirmatory rephrasing</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>oral communication pace</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>"coming alongside" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:044077</t>
+          <t>BCIO:044125</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>script-based communication</t>
-        </is>
-      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>tone of voice</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
+          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:044035</t>
+          <t>BCIO:044127</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>communication inviting reactions to content presented</t>
-        </is>
-      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>object visual style</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A communication seeking information about a person's responses to the  content presented.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>asking for opinions</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:044065</t>
+          <t>BCIO:044128</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>negotiation</t>
-        </is>
-      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>source visual style</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
+          <t>An attribute of an intervention person source concerning how they appear to others.</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>may be purposefully chosen to convey certain attributes of the source</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:044040</t>
+          <t>BCIO:044004</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>communication involving elaboration of arguments</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>communication style</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
+          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:044060</t>
+          <t>BCIO:044123</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>guiding communication</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>warm communication style</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
+          <t>A communication style which demonstrates human interest and caring.</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>friendly communication style</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:044037</t>
+          <t>BCIO:044096</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>communication involving agreement</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>controlling communication style</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A communication in which one participant concurs with the views stated by another.</t>
+          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:044038</t>
+          <t>BCIO:044110</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1530,143 +1460,140 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>communication involving agreement followed by highlighting incongruent aspects</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>non-defensive communication style</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>"agreement with a twist" in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
+          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:044022</t>
+          <t>BCIO:044108</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>communication adding intensity to another's views</t>
-        </is>
-      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>interactive communication style</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>"overshooting" in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+          <t>A communication style characterised by being responsive to the recipient's activity.</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>interactive presentation</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:044029</t>
+          <t>BCIO:044087</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>communication evoking another's ideas about change</t>
-        </is>
-      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>communication style conveying acceptance</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>evoking change talk in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:044050</t>
+          <t>BCIO:044118</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>communication using particular language</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>responsive communication style</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>A communication using certain vocabulary or phraseology.</t>
+          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:044055</t>
+          <t>BCIO:044116</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1674,32 +1601,36 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>communication avoiding offensive language</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>relaxed communication style</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
+          <t>A communication style characterised by a lack of tension or anxiety.</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+          <t>calm communication style</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:044051</t>
+          <t>BCIO:050380</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1707,32 +1638,32 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>communication using neutral language</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>aggressive communication style</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
+          <t>A communication style characterised by aggression.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:044056</t>
+          <t>BCIO:044104</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1740,32 +1671,32 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>communication using selected words from a second language</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>formal communication style</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
+          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:044054</t>
+          <t>BCIO:044091</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1773,36 +1704,36 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>communication using specialist language</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>communication style conveying hopefulness</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>using jargon</t>
-        </is>
-      </c>
+          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
+          <t>optimism, positivity</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:044052</t>
+          <t>BCIO:044117</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1810,32 +1741,41 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>communication using non-pressurising language</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>respectful communication style</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
+          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>"acknowledging the victim's feelings"</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:044053</t>
+          <t>BCIO:044111</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1843,65 +1783,65 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>communication using slang</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>non-confrontational communication style</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>A communication using informal language shared by members of a particular community.</t>
+          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:044012</t>
+          <t>BCIO:044092</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>asking questions</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>communication style conveying perceived superiority</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>A communication in which some participant requests information from another participant.</t>
+          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:044014</t>
+          <t>BCIO:050389</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1909,32 +1849,37 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>asking focused questions</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>direct communication style</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
+          <t>A communication style characterised by the explicit presentation of information.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Note that this class is different from directive communication style</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:050382</t>
+          <t>BCIO:044109</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1942,32 +1887,41 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>asking clarifying questions</t>
-        </is>
-      </c>
+      <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>legitimising communication style</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Asking questions in order to better understand an issue.</t>
+          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+          <t>validating emotions</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:044016</t>
+          <t>BCIO:044107</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1975,32 +1929,32 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>asking open-ended questions</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>intellectual communication style</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
+          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:044015</t>
+          <t>BCIO:044115</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2008,36 +1962,32 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>asking leading questions</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>polite communication style</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>asking directive questions</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+          <t>A communication style characterised by courtesy.</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:044013</t>
+          <t>BCIO:044105</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2045,177 +1995,164 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>asking closed-ended questions</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>impatient communication style</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Asking questions that can only be answered with a limited set of responses.</t>
+          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:044010</t>
+          <t>BCIO:044079</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>affirming communication</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>active participation encouraging communication style</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
+          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Making explicit statements of partnership or support; Shows approval;</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:044048</t>
+          <t>BCIO:050390</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>communication using deliberate pauses</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>humorous communication style</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
+          <t>A communication style intended to amuse.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
-          <t>staying silent (where this is intended to give others the chance to speak)</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:044041</t>
+          <t>BCIO:044131</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>communication offering choice</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>anxious communication style</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A communication involving the initiator offering a range of options to the recipient.</t>
+          <t>A communication style characterised by nervousness or unease.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:050388</t>
+          <t>BCIO:050381</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>communication showing acknowledgement</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>angry communication style</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A communication involving the expressed recognition of what another has expressed.</t>
+          <t>A communication style characterised by anger.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:044021</t>
+          <t>BCIO:044085</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2223,244 +2160,247 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>communication acknowledging difficulties</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>collaborative communication style</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
+          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:044047</t>
+          <t>BCIO:044122</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>communication using commands</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>verbally dominant communication style</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>communication using imperatives</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
+          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:044036</t>
+          <t>BCIO:044114</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>persuasive communication style</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
+          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>From Motivational Interviewing</t>
-        </is>
-      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:044059</t>
+          <t>BCIO:044094</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>emotionally expressive communication</t>
-        </is>
-      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>communication style conveying support for change</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
+          <t>A communication style which imparts one's belief that the recipient can change.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:044058</t>
+          <t>BCIO:044000</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>communication using rational arguments</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>behaviour change intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
+          <t>A communication style that is an attribute of a BCI content communication process.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:044061</t>
+          <t>BCIO:044119</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>interrupting</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>semi-structured communication style</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>A communication in which one person interjects before another has finished making their point.</t>
+          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+          <t>organised communication style</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:044001</t>
+          <t>BCIO:044082</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>intervention content communication process</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>articulate communication style</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A communication that transmits the content of an intervention</t>
+          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
-        </is>
-      </c>
+          <t>fluent</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:044002</t>
+          <t>BCIO:044102</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2468,303 +2408,284 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>behaviour change intervention content communication process</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>engaging communication style</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>An intervention content communication process that is about behaviour change intervention content</t>
+          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:044124</t>
+          <t>BCIO:044086</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>relationship building</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>cold communication style</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
+          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
-          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:044028</t>
+          <t>BCIO:044120</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>communication encouraging discussion</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>structured communication style</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
+          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
+          <t>standardised</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>Contrasts with a more one-way, didactic style</t>
+          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:044018</t>
+          <t>BCIO:044112</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>branded communication</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>non-judgmental communication style</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>use of branding; brand identity</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
+          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Change for Life, Time to Change, NHS Smokefree</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:044023</t>
+          <t>BCIO:044090</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>communication asking permission to provide information and advice</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>communication style conveying genuineness</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
+          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
+          <t>sincerity</t>
+        </is>
+      </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:044062</t>
+          <t>BCIO:044101</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>communication avoiding interrupting</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>empathic communication style</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
+          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+          <t>sensitivity, compassion</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:044034</t>
+          <t>BCIO:044103</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>communication highlighting a contradiction</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>entertaining communication style</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
+          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
-        </is>
-      </c>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:044030</t>
+          <t>BCIO:050392</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>exploring communication</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>rushed communication style</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
+          <t>A communication style conveying information in a hurried way.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
-          <t>eliciting or seeking information</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:050385</t>
+          <t>BCIO:044113</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2772,37 +2693,36 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about an experience</t>
-        </is>
-      </c>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>patient communication style</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to an experience.</t>
+          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
+      <c r="M68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>"willing to listen"</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:050386</t>
+          <t>BCIO:044084</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2810,36 +2730,41 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about a topic</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>autonomy-supportive communication style</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about a matter.</t>
+          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
+          <t>needs-supportive communication style</t>
+        </is>
+      </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>clarifying what someone has said</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>from Self-Determination Theory interventions.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:050383</t>
+          <t>BCIO:044083</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2847,36 +2772,41 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about a topic</t>
-        </is>
-      </c>
+      <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>attentive communication style</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to a matter.</t>
+          <t>A communication style characterised by purposeful consideration of another's statements.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Elicit concerns, problems and reactions</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>"listened carefully to what you had to say"</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:050387</t>
+          <t>BCIO:044098</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2884,108 +2814,102 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about an experience</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>didactic communication style</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about an experience.</t>
+          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
+      <c r="M71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>gave a short lecture, conference presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:044026</t>
+          <t>BCIO:044095</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>communication checking for others' understanding</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>communication style demonstrating positive regard</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
+          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:044043</t>
+          <t>BCIO:050391</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>communication using a particular form of address</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>non-responsive communication style</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
+          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
-        </is>
-      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:044044</t>
+          <t>BCIO:044106</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2993,32 +2917,37 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>communication using formal address</t>
-        </is>
-      </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>informal communication style</t>
+        </is>
+      </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
+          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:044045</t>
+          <t>BCIO:044097</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -3026,32 +2955,32 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>communication using informal address</t>
-        </is>
-      </c>
+      <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>conversational communication style</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
+          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:044046</t>
+          <t>BCIO:044121</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3059,285 +2988,291 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>communication using preferred form of address</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>theatrical communication style</t>
+        </is>
+      </c>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
+          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:044078</t>
+          <t>BCIO:044089</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>shifting focus of communication</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>communication style conveying concern</t>
+        </is>
+      </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
+          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:044042</t>
+          <t>BCIO:044081</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>communication understating intensity of person's views</t>
-        </is>
-      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>aloof communication style</t>
+        </is>
+      </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>"undershooting" in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
+          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:044070</t>
+          <t>BCIO:044100</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>paraphrasing</t>
-        </is>
-      </c>
+      <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>easily comprehended communication style</t>
+        </is>
+      </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>A communication in which one participant summarises what the other said.</t>
+          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>using non-technical language, using clear language, avoiding jargon</t>
+        </is>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
+          <t>This can involve using plain and simple language</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:044049</t>
+          <t>BCIO:044099</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>communication using interjections to signal attentiveness</t>
-        </is>
-      </c>
+      <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>directive communication style</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>A communication style intended to play an active role in another person's decision making.</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Words like "interesting", "yeah"," mmhmm"</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
+          <t>Note that this class is different from direct communication style</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:044027</t>
+          <t>BCIO:044005</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>communication checking for own understanding</t>
-        </is>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
+          <t>A communication style that is an attribute of an intervention content communication process.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>clarifying what another has said</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:044024</t>
+          <t>BCIO:050384</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>communication avoiding argumentation</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
+          <t>A process involving the transmission of information between two or more participants.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>BCIO:044009</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>process profile</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>active listening</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
-        </is>
-      </c>
+          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:044065</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3346,7 +3281,7 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>process attribute</t>
+          <t>negotiation</t>
         </is>
       </c>
       <c r="G84" t="inlineStr"/>
@@ -3355,52 +3290,60 @@
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
-        </is>
-      </c>
+          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:044003</t>
+          <t>BCIO:044001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>communication process attribute</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>intervention content communication process</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>An attribute of a communication process.</t>
+          <t>A communication that transmits the content of an intervention</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
+          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:044129</t>
+          <t>BCIO:044002</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3408,182 +3351,174 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>object layout</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>behaviour change intervention content communication process</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
+          <t>An intervention content communication process that is about behaviour change intervention content</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
-          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
+          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:044004</t>
+          <t>BCIO:044034</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>communication highlighting a contradiction</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>communication style</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
+          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:044107</t>
+          <t>BCIO:044059</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>emotionally expressive communication</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>intellectual communication style</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
+          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:044094</t>
+          <t>BCIO:044061</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>interrupting</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>communication style conveying support for change</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>A communication style which imparts one's belief that the recipient can change.</t>
+          <t>A communication in which one person interjects before another has finished making their point.</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:044100</t>
+          <t>BCIO:044037</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>communication involving agreement</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>easily comprehended communication style</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
+          <t>A communication in which one participant concurs with the views stated by another.</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
-          <t>using non-technical language, using clear language, avoiding jargon</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>This can involve using plain and simple language</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:044116</t>
+          <t>BCIO:044038</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3591,187 +3526,189 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>communication involving agreement followed by highlighting incongruent aspects</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>relaxed communication style</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of tension or anxiety.</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>calm communication style</t>
-        </is>
-      </c>
+          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
+          <t>"agreement with a twist" in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:044110</t>
+          <t>BCIO:044049</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>communication using interjections to signal attentiveness</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>non-defensive communication style</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
+          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Words like "interesting", "yeah"," mmhmm"</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:044099</t>
+          <t>BCIO:044042</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>communication understating intensity of person's views</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>directive communication style</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>A communication style intended to play an active role in another person's decision making.</t>
+          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>"undershooting" in motivational interviewing</t>
+        </is>
+      </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>Note that this class is different from direct communication style</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:044005</t>
+          <t>BCIO:044011</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>agenda-sharing communication</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of an intervention content communication process.</t>
+          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
-        </is>
-      </c>
+          <t>agenda mapping</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:044106</t>
+          <t>BCIO:050388</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>communication showing acknowledgement</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>informal communication style</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
+          <t>A communication involving the expressed recognition of what another has expressed.</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:044119</t>
+          <t>BCIO:044021</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3779,77 +3716,65 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>communication acknowledging difficulties</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>semi-structured communication style</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>organised communication style</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
+          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:044091</t>
+          <t>BCIO:044071</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>reflective communication</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>communication style conveying hopefulness</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>optimism, positivity</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
+          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:044118</t>
+          <t>BCIO:044076</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3857,37 +3782,36 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>re-evaluation prompting reflective communication</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>responsive communication style</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
+          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
-        </is>
-      </c>
+          <t>"amplified reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:044087</t>
+          <t>BCIO:044072</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3895,32 +3819,36 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>summarising reflective communication</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>communication style conveying acceptance</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
+          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
+          <t>"summarising reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:044089</t>
+          <t>BCIO:044073</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3928,32 +3856,36 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>double-sided reflective communication</t>
+        </is>
+      </c>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>communication style conveying concern</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
+          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
+          <t>"double-sided reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:044115</t>
+          <t>BCIO:044075</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3961,32 +3893,36 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>emotion-emphasising reflective communication</t>
+        </is>
+      </c>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>polite communication style</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>A communication style characterised by courtesy.</t>
+          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
+          <t>"reflection of feeling" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:044109</t>
+          <t>BCIO:044074</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -3994,257 +3930,274 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>metaphor-using reflective communication</t>
+        </is>
+      </c>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>legitimising communication style</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>validating emotions</t>
-        </is>
-      </c>
+          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr">
-        <is>
-          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
-        </is>
-      </c>
+          <t>"metaphorical reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:044081</t>
+          <t>BCIO:044028</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>communication encouraging discussion</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>aloof communication style</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
+          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Contrasts with a more one-way, didactic style</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:044092</t>
+          <t>BCIO:044036</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>communication style conveying perceived superiority</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
+          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>From Motivational Interviewing</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:044084</t>
+          <t>BCIO:044069</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>offering reassurance</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>autonomy-supportive communication style</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>needs-supportive communication style</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
+          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>made reassuring statements</t>
+        </is>
+      </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>from Self-Determination Theory interventions.</t>
+          <t>based on Roter Interactional Analysis System</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:044112</t>
+          <t>BCIO:044018</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>branded communication</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>non-judgmental communication style</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
+          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
+          <t>use of branding; brand identity</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Change for Life, Time to Change, NHS Smokefree</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:044000</t>
+          <t>BCIO:044022</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>communication adding intensity to another's views</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>behaviour change intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of a BCI content communication process.</t>
+          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
-        </is>
-      </c>
+          <t>"overshooting" in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:044108</t>
+          <t>BCIO:044030</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>exploring communication</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>interactive communication style</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>A communication style characterised by being responsive to the recipient's activity.</t>
+          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
       <c r="O108" t="inlineStr">
         <is>
-          <t>interactive presentation</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>eliciting or seeking information</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:044104</t>
+          <t>BCIO:050383</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4252,32 +4205,36 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about a topic</t>
+        </is>
+      </c>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>formal communication style</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
+          <t>An exploring communication focused on a person's affective responses to a matter.</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Elicit concerns, problems and reactions</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:044097</t>
+          <t>BCIO:050387</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4285,32 +4242,37 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about an experience</t>
+        </is>
+      </c>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>conversational communication style</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
+          <t>An exploring communication focused on what a person thinks about an experience.</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:044085</t>
+          <t>BCIO:050386</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4318,32 +4280,36 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about a topic</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>collaborative communication style</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
+          <t>An exploring communication focused on what a person thinks about a matter.</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>clarifying what someone has said</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:044105</t>
+          <t>BCIO:050385</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4351,285 +4317,290 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about an experience</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>impatient communication style</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
+          <t>An exploring communication focused on a person's affective responses to an experience.</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:044123</t>
+          <t>BCIO:044058</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>communication using rational arguments</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>warm communication style</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>A communication style which demonstrates human interest and caring.</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>friendly communication style</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
+          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:050390</t>
+          <t>BCIO:044029</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>communication evoking another's ideas about change</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>humorous communication style</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>A communication style intended to amuse.</t>
+          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
+          <t>evoking change talk in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:044111</t>
+          <t>BCIO:044048</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>communication using deliberate pauses</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>non-confrontational communication style</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
+          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>staying silent (where this is intended to give others the chance to speak)</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:044101</t>
+          <t>BCIO:044035</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>communication inviting reactions to content presented</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>empathic communication style</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>sensitivity, compassion</t>
-        </is>
-      </c>
+          <t>A communication seeking information about a person's responses to the  content presented.</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
+          <t>asking for opinions</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:050389</t>
+          <t>BCIO:044070</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>paraphrasing</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>direct communication style</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>A communication style characterised by the explicit presentation of information.</t>
+          <t>A communication in which one participant summarises what the other said.</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Note that this class is different from directive communication style</t>
+          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:044083</t>
+          <t>BCIO:044040</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>communication involving elaboration of arguments</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>attentive communication style</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>A communication style characterised by purposeful consideration of another's statements.</t>
+          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
       <c r="O118" t="inlineStr">
         <is>
-          <t>"listened carefully to what you had to say"</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:044079</t>
+          <t>BCIO:044050</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>communication using particular language</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>active participation encouraging communication style</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
+          <t>A communication using certain vocabulary or phraseology.</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:050392</t>
+          <t>BCIO:044052</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4637,32 +4608,32 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>communication using non-pressurising language</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>rushed communication style</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>A communication style conveying information in a hurried way.</t>
+          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:044113</t>
+          <t>BCIO:044055</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4670,36 +4641,32 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>communication avoiding offensive language</t>
+        </is>
+      </c>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>patient communication style</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
+          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
       <c r="O121" t="inlineStr">
         <is>
-          <t>"willing to listen"</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:044103</t>
+          <t>BCIO:044051</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4707,36 +4674,32 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>communication using neutral language</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>entertaining communication style</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>fun</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
+          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:044122</t>
+          <t>BCIO:044053</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4744,32 +4707,32 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>communication using slang</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>verbally dominant communication style</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
+          <t>A communication using informal language shared by members of a particular community.</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:050391</t>
+          <t>BCIO:044054</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4777,32 +4740,36 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>communication using specialist language</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>non-responsive communication style</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
+          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+          <t>using jargon</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:044090</t>
+          <t>BCIO:044056</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4810,102 +4777,103 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>communication using selected words from a second language</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>communication style conveying genuineness</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>sincerity</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
+          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:050380</t>
+          <t>BCIO:044026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>communication checking for others' understanding</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>aggressive communication style</t>
-        </is>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>A communication style characterised by aggression.</t>
+          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:044086</t>
+          <t>BCIO:044019</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>discussion</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>cold communication style</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
+          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:044121</t>
+          <t>BCIO:044020</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4913,355 +4881,355 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>classroom-style discussion</t>
+        </is>
+      </c>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>theatrical communication style</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
+          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:044095</t>
+          <t>BCIO:044017</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>banter</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>communication style demonstrating positive regard</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
+          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:044120</t>
+          <t>BCIO:044064</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>narrative communication</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>structured communication style</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr">
-        <is>
-          <t>standardised</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr">
-        <is>
-          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
-        </is>
-      </c>
+          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:044082</t>
+          <t>BCIO:044010</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>affirming communication</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>articulate communication style</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>fluent</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
+          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Making explicit statements of partnership or support; Shows approval;</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:050381</t>
+          <t>BCIO:044023</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>communication asking permission to provide information and advice</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>angry communication style</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>A communication style characterised by anger.</t>
+          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:044098</t>
+          <t>BCIO:044060</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>guiding communication</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>didactic communication style</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
+          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
-          <t>gave a short lecture, conference presentation</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:044131</t>
+          <t>BCIO:044024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>communication avoiding argumentation</t>
+        </is>
+      </c>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>anxious communication style</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>A communication style characterised by nervousness or unease.</t>
+          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:044114</t>
+          <t>BCIO:044047</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>communication using commands</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>persuasive communication style</t>
-        </is>
-      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
+          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
+          <t>communication using imperatives</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:044117</t>
+          <t>BCIO:044041</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>communication offering choice</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>respectful communication style</t>
-        </is>
-      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
+          <t>A communication involving the initiator offering a range of options to the recipient.</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
-          <t>"acknowledging the victim's feelings"</t>
-        </is>
-      </c>
-      <c r="Q136" t="inlineStr">
-        <is>
-          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:044096</t>
+          <t>BCIO:044043</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>communication using a particular form of address</t>
+        </is>
+      </c>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>controlling communication style</t>
-        </is>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
+          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:044102</t>
+          <t>BCIO:044046</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -5269,32 +5237,36 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>communication using preferred form of address</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>engaging communication style</t>
-        </is>
-      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
+          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:044128</t>
+          <t>BCIO:044044</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
@@ -5302,41 +5274,32 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>source visual style</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>communication using formal address</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>An attribute of an intervention person source concerning how they appear to others.</t>
+          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
-          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>may be purposefully chosen to convey certain attributes of the source</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:044127</t>
+          <t>BCIO:044045</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -5344,164 +5307,176 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>object visual style</t>
-        </is>
-      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>communication using informal address</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
+          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:044126</t>
+          <t>BCIO:044027</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>communication checking for own understanding</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>oral communication pace</t>
-        </is>
-      </c>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
+          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>clarifying what another has said</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:044130</t>
+          <t>BCIO:044039</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>communication involving confirmatory rephrasing</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>readability</t>
-        </is>
-      </c>
+      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
+          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr"/>
+          <t>"coming alongside" in Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:044125</t>
+          <t>BCIO:044124</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>relationship building</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>tone of voice</t>
-        </is>
-      </c>
+      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
+          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>BCIO:044062</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>communication avoiding interrupting</t>
+        </is>
+      </c>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organism participates.</t>
-        </is>
-      </c>
+          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:036000</t>
+          <t>BCIO:044077</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
@@ -5510,7 +5485,7 @@
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>individual human behaviour</t>
+          <t>script-based communication</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
@@ -5519,72 +5494,93 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
+          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:050441</t>
+          <t>BCIO:044078</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>socially-related behaviour</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>shifting focus of communication</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to the social environment.</t>
-        </is>
-      </c>
+          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:036025</t>
+          <t>BCIO:044012</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>asking questions</t>
+        </is>
+      </c>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>inter-personal behaviour</t>
-        </is>
-      </c>
+      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
+          <t>A communication in which some participant requests information from another participant.</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:036034</t>
+          <t>BCIO:044014</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5592,32 +5588,32 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>human communication behaviour</t>
-        </is>
-      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>asking focused questions</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
+          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:050237</t>
+          <t>BCIO:044013</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5625,32 +5621,32 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>asking closed-ended questions</t>
+        </is>
+      </c>
       <c r="H149" t="inlineStr"/>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>linguistic communication behaviour</t>
-        </is>
-      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
+          <t>Asking questions that can only be answered with a limited set of responses.</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BCIO:050457</t>
+          <t>BCIO:044015</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5660,7 +5656,7 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>expressive behaviour</t>
+          <t>asking leading questions</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
@@ -5668,22 +5664,26 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>An individual human behaviour that conveys a thought or feeling.</t>
+          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
+          <t>asking directive questions</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BCIO:050374</t>
+          <t>BCIO:044016</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5691,60 +5691,60 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>laughing</t>
-        </is>
-      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>asking open-ended questions</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
+          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BCIO:050552</t>
+          <t>BCIO:050382</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>communication channel</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>asking clarifying questions</t>
+        </is>
+      </c>
       <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; by which a communication is delivered.</t>
+          <t>Asking questions in order to better understand an issue.</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5817,7 +5817,7 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
@@ -5859,7 +5859,7 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>human being</t>
+          <t>person</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -5896,13 +5896,13 @@
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5929,13 +5929,13 @@
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5958,7 +5958,7 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
@@ -6012,13 +6012,13 @@
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/StyleOfDelivery/BCIO-style-hierarchy.xlsx
+++ b/StyleOfDelivery/BCIO-style-hierarchy.xlsx
@@ -442,32 +442,32 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>crossreference</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
         <is>
           <t>synonyms</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>examples</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>comment</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>BCIO:050384</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -582,7 +582,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>bodily process</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -592,14 +592,27 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organism participates.</t>
-        </is>
-      </c>
+          <t>A process involving the transmission of information between two or more participants.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:036000</t>
+          <t>BCIO:044069</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -608,7 +621,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>individual human behaviour</t>
+          <t>offering reassurance</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -617,171 +630,213 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
-        </is>
-      </c>
+          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>based on Roter Interactional Analysis System</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>made reassuring statements</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:050457</t>
+          <t>BCIO:044039</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>expressive behaviour</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>communication involving confirmatory rephrasing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>An individual human behaviour that conveys a thought or feeling.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>"coming alongside" in Motivational Interviewing</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:036034</t>
+          <t>BCIO:044035</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>communication inviting reactions to content presented</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>human communication behaviour</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>A communication seeking information about a person's responses to the  content presented.</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>asking for opinions</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:050237</t>
+          <t>BCIO:044011</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>agenda-sharing communication</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>linguistic communication behaviour</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>agenda mapping</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:050374</t>
+          <t>BCIO:044065</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>negotiation</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>laughing</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050441</t>
+          <t>BCIO:044043</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>socially-related behaviour</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>communication using a particular form of address</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to the social environment.</t>
-        </is>
-      </c>
+          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:036025</t>
+          <t>BCIO:044045</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -789,189 +844,210 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>inter-personal behaviour</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>communication using informal address</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>BCIO:044046</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>communication using preferred form of address</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
-        </is>
-      </c>
+          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:045000</t>
+          <t>BCIO:044044</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>intervention delivery</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>communication using formal address</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A planned process by which intervention content is delivered.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:008000</t>
+          <t>BCIO:044009</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>behaviour change intervention delivery</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>active listening</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:044007</t>
+          <t>BCIO:044027</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>participant-led intervention delivery</t>
-        </is>
-      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>communication checking for own understanding</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>clarifying what another has said</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:044008</t>
+          <t>BCIO:044019</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>source-led intervention delivery</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>discussion</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:044006</t>
+          <t>BCIO:044020</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -981,7 +1057,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>person-centred intervention delivery</t>
+          <t>classroom-style discussion</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -989,80 +1065,105 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:050552</t>
+          <t>BCIO:044010</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>communication channel</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>affirming communication</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; by which a communication is delivered.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Making explicit statements of partnership or support; Shows approval;</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>BCIO:044049</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>process profile</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>communication using interjections to signal attentiveness</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
+          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Words like "interesting", "yeah"," mmhmm"</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:044047</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1071,7 +1172,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>process attribute</t>
+          <t>communication using commands</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1080,52 +1181,59 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
+          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>communication using imperatives</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:044003</t>
+          <t>BCIO:044050</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>communication process attribute</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>communication using particular language</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>An attribute of a communication process.</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>A communication using certain vocabulary or phraseology.</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
-        </is>
-      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:044130</t>
+          <t>BCIO:044055</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1133,36 +1241,32 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>readability</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>communication avoiding offensive language</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:044129</t>
+          <t>BCIO:044052</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1170,41 +1274,32 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>object layout</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>communication using non-pressurising language</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:044126</t>
+          <t>BCIO:044051</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1212,32 +1307,32 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>oral communication pace</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>communication using neutral language</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:044125</t>
+          <t>BCIO:044053</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1245,32 +1340,32 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>tone of voice</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>communication using slang</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+          <t>A communication using informal language shared by members of a particular community.</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:044127</t>
+          <t>BCIO:044054</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1278,36 +1373,36 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>object visual style</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>communication using specialist language</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>using jargon</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:044128</t>
+          <t>BCIO:044056</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1315,144 +1410,139 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>source visual style</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>communication using selected words from a second language</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>An attribute of an intervention person source concerning how they appear to others.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>may be purposefully chosen to convey certain attributes of the source</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:044004</t>
+          <t>BCIO:044124</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>relationship building</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>communication style</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:044123</t>
+          <t>BCIO:044042</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>communication understating intensity of person's views</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>warm communication style</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A communication style which demonstrates human interest and caring.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>friendly communication style</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>"undershooting" in motivational interviewing</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:044096</t>
+          <t>BCIO:044012</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>asking questions</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>controlling communication style</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>A communication in which some participant requests information from another participant.</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:044110</t>
+          <t>BCIO:050382</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1460,32 +1550,32 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>asking clarifying questions</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>non-defensive communication style</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>Asking questions in order to better understand an issue.</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:044108</t>
+          <t>BCIO:044014</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1493,36 +1583,32 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>asking focused questions</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>interactive communication style</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>A communication style characterised by being responsive to the recipient's activity.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>interactive presentation</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:044087</t>
+          <t>BCIO:044015</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1530,32 +1616,36 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>asking leading questions</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>communication style conveying acceptance</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>asking directive questions</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:044118</t>
+          <t>BCIO:044016</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1563,37 +1653,32 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>asking open-ended questions</t>
+        </is>
+      </c>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>responsive communication style</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:044116</t>
+          <t>BCIO:044013</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1601,102 +1686,112 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>asking closed-ended questions</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>relaxed communication style</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of tension or anxiety.</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>calm communication style</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
+          <t>Asking questions that can only be answered with a limited set of responses.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:050380</t>
+          <t>BCIO:044028</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>communication encouraging discussion</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>aggressive communication style</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A communication style characterised by aggression.</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Contrasts with a more one-way, didactic style</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:044104</t>
+          <t>BCIO:044030</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>exploring communication</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>formal communication style</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
+          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>eliciting or seeking information</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:044091</t>
+          <t>BCIO:050385</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1704,36 +1799,37 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about an experience</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>communication style conveying hopefulness</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>optimism, positivity</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
+          <t>An exploring communication focused on a person's affective responses to an experience.</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:044117</t>
+          <t>BCIO:050387</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1741,41 +1837,37 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about an experience</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>respectful communication style</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
+          <t>An exploring communication focused on what a person thinks about an experience.</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>"acknowledging the victim's feelings"</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:044111</t>
+          <t>BCIO:050386</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1783,32 +1875,36 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about a topic</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>non-confrontational communication style</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>An exploring communication focused on what a person thinks about a matter.</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>clarifying what someone has said</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:044092</t>
+          <t>BCIO:050383</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1816,310 +1912,317 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about a topic</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>communication style conveying perceived superiority</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+          <t>An exploring communication focused on a person's affective responses to a matter.</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Elicit concerns, problems and reactions</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:050389</t>
+          <t>BCIO:044024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>communication avoiding argumentation</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>direct communication style</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A communication style characterised by the explicit presentation of information.</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Note that this class is different from directive communication style</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:044109</t>
+          <t>BCIO:044060</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>guiding communication</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>legitimising communication style</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>validating emotions</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
-        </is>
-      </c>
+          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:044107</t>
+          <t>BCIO:044077</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>script-based communication</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>intellectual communication style</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:044115</t>
+          <t>BCIO:044059</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>emotionally expressive communication</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>polite communication style</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>A communication style characterised by courtesy.</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:044105</t>
+          <t>BCIO:044040</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>communication involving elaboration of arguments</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>impatient communication style</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:044079</t>
+          <t>BCIO:044018</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>branded communication</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>active participation encouraging communication style</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Change for Life, Time to Change, NHS Smokefree</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>use of branding; brand identity</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:050390</t>
+          <t>BCIO:044026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>communication checking for others' understanding</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>humorous communication style</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A communication style intended to amuse.</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
+          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr"/>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:044131</t>
+          <t>BCIO:044071</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>reflective communication</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>anxious communication style</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A communication style characterised by nervousness or unease.</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:050381</t>
+          <t>BCIO:044076</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2127,32 +2230,36 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>re-evaluation prompting reflective communication</t>
+        </is>
+      </c>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>angry communication style</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A communication style characterised by anger.</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
+          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr"/>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>"amplified reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:044085</t>
+          <t>BCIO:044074</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2160,32 +2267,36 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>metaphor-using reflective communication</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>collaborative communication style</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
+          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr"/>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>"metaphorical reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:044122</t>
+          <t>BCIO:044075</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2193,32 +2304,36 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>emotion-emphasising reflective communication</t>
+        </is>
+      </c>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>verbally dominant communication style</t>
-        </is>
-      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>"reflection of feeling" in Motivational Interviewing</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:044114</t>
+          <t>BCIO:044073</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2226,32 +2341,36 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>double-sided reflective communication</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>persuasive communication style</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
+          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr"/>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>"double-sided reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:044094</t>
+          <t>BCIO:044072</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2259,148 +2378,143 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>summarising reflective communication</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>communication style conveying support for change</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>A communication style which imparts one's belief that the recipient can change.</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr"/>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>"summarising reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:044000</t>
+          <t>BCIO:044022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>communication adding intensity to another's views</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>behaviour change intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of a BCI content communication process.</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr"/>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
+          <t>"overshooting" in motivational interviewing</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:044119</t>
+          <t>BCIO:044029</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>communication evoking another's ideas about change</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>semi-structured communication style</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>organised communication style</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>evoking change talk in motivational interviewing</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:044082</t>
+          <t>BCIO:050388</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>communication showing acknowledgement</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>articulate communication style</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>fluent</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr"/>
+          <t>A communication involving the expressed recognition of what another has expressed.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:044102</t>
+          <t>BCIO:044021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2408,405 +2522,395 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>communication acknowledging difficulties</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>engaging communication style</t>
-        </is>
-      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
+          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr"/>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:044086</t>
+          <t>BCIO:044048</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>communication using deliberate pauses</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>cold communication style</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
+          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr"/>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>staying silent (where this is intended to give others the chance to speak)</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:044120</t>
+          <t>BCIO:044070</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>paraphrasing</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>structured communication style</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>standardised</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
-        </is>
-      </c>
+          <t>A communication in which one participant summarises what the other said.</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:044112</t>
+          <t>BCIO:044064</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>narrative communication</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>non-judgmental communication style</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
+          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr"/>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:044090</t>
+          <t>BCIO:044061</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>interrupting</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>communication style conveying genuineness</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>sincerity</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr"/>
+          <t>A communication in which one person interjects before another has finished making their point.</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:044101</t>
+          <t>BCIO:044023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>communication asking permission to provide information and advice</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>empathic communication style</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>sensitivity, compassion</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr"/>
+          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:044103</t>
+          <t>BCIO:044034</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>communication highlighting a contradiction</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>entertaining communication style</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>fun</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
+          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:050392</t>
+          <t>BCIO:044036</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>rushed communication style</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>A communication style conveying information in a hurried way.</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
+          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>From Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr"/>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:044113</t>
+          <t>BCIO:044017</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>banter</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>patient communication style</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
+          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>"willing to listen"</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:044084</t>
+          <t>BCIO:044078</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>shifting focus of communication</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>autonomy-supportive communication style</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>needs-supportive communication style</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>from Self-Determination Theory interventions.</t>
-        </is>
-      </c>
+          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:044083</t>
+          <t>BCIO:044037</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>communication involving agreement</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>attentive communication style</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>A communication style characterised by purposeful consideration of another's statements.</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
+          <t>A communication in which one participant concurs with the views stated by another.</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr"/>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>"listened carefully to what you had to say"</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:044098</t>
+          <t>BCIO:044038</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2814,173 +2918,173 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>communication involving agreement followed by highlighting incongruent aspects</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>didactic communication style</t>
-        </is>
-      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
+          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr"/>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>gave a short lecture, conference presentation</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>"agreement with a twist" in motivational interviewing</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:044095</t>
+          <t>BCIO:044041</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>communication offering choice</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>communication style demonstrating positive regard</t>
-        </is>
-      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
+          <t>A communication involving the initiator offering a range of options to the recipient.</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:050391</t>
+          <t>BCIO:044058</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>communication using rational arguments</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>non-responsive communication style</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
+          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr"/>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:044106</t>
+          <t>BCIO:044062</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>communication avoiding interrupting</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>informal communication style</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr"/>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
-        </is>
-      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:044097</t>
+          <t>BCIO:044001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>intervention content communication process</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>conversational communication style</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
+          <t>A communication that transmits the content of an intervention</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr"/>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:044121</t>
+          <t>BCIO:044002</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2988,98 +3092,87 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>behaviour change intervention content communication process</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>theatrical communication style</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
+          <t>An intervention content communication process that is about behaviour change intervention content</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr"/>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BCIO:044089</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>communication style conveying concern</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr"/>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:044081</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>process attribute</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>aloof communication style</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr"/>
+          <t>A process profile that is an attribute of a process.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:044100</t>
+          <t>BCIO:044003</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3087,41 +3180,37 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>communication process attribute</t>
+        </is>
+      </c>
       <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>easily comprehended communication style</t>
-        </is>
-      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
+          <t>An attribute of a communication process.</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr"/>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>using non-technical language, using clear language, avoiding jargon</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>This can involve using plain and simple language</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:044099</t>
+          <t>BCIO:044126</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3130,40 +3219,31 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>directive communication style</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>oral communication pace</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>A communication style intended to play an active role in another person's decision making.</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
+          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr"/>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>Note that this class is different from direct communication style</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:044005</t>
+          <t>BCIO:044127</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3172,178 +3252,181 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>object visual style</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of an intervention content communication process.</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
+          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr"/>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:050384</t>
+          <t>BCIO:044004</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>communication</t>
-        </is>
-      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>communication style</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>A process involving the transmission of information between two or more participants.</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
+          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr"/>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
-        </is>
-      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:044009</t>
+          <t>BCIO:044100</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>active listening</t>
-        </is>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>easily comprehended communication style</t>
+        </is>
+      </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
+          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>This can involve using plain and simple language</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr"/>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr"/>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>using non-technical language, using clear language, avoiding jargon</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:044065</t>
+          <t>BCIO:044081</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>negotiation</t>
-        </is>
-      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>aloof communication style</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
+          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr"/>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:044001</t>
+          <t>BCIO:044005</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>intervention content communication process</t>
-        </is>
-      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>A communication that transmits the content of an intervention</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+          <t>A communication style that is an attribute of an intervention content communication process.</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr"/>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
-        </is>
-      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:044002</t>
+          <t>BCIO:044096</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3351,174 +3434,172 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>behaviour change intervention content communication process</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>controlling communication style</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>An intervention content communication process that is about behaviour change intervention content</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
+          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr"/>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
-        </is>
-      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:044034</t>
+          <t>BCIO:044092</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>communication highlighting a contradiction</t>
-        </is>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>communication style conveying perceived superiority</t>
+        </is>
+      </c>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
+          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
-        </is>
-      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:044059</t>
+          <t>BCIO:044103</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>emotionally expressive communication</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>entertaining communication style</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
+          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr"/>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>fun</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:044061</t>
+          <t>BCIO:044082</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>interrupting</t>
-        </is>
-      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>articulate communication style</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>A communication in which one person interjects before another has finished making their point.</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
+          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr"/>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>fluent</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:044037</t>
+          <t>BCIO:044089</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>communication involving agreement</t>
-        </is>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>communication style conveying concern</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>A communication in which one participant concurs with the views stated by another.</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
+          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr"/>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:044038</t>
+          <t>BCIO:044106</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3526,189 +3607,187 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>communication involving agreement followed by highlighting incongruent aspects</t>
-        </is>
-      </c>
+      <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>informal communication style</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>"agreement with a twist" in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr"/>
+          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:044049</t>
+          <t>BCIO:044085</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>communication using interjections to signal attentiveness</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>collaborative communication style</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Words like "interesting", "yeah"," mmhmm"</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:044042</t>
+          <t>BCIO:044117</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>communication understating intensity of person's views</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>respectful communication style</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>"undershooting" in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr"/>
+          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>"acknowledging the victim's feelings"</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:044011</t>
+          <t>BCIO:050389</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>agenda-sharing communication</t>
-        </is>
-      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>direct communication style</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>agenda mapping</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P94" t="inlineStr"/>
+          <t>A communication style characterised by the explicit presentation of information.</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Note that this class is different from directive communication style</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:050388</t>
+          <t>BCIO:044090</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>communication showing acknowledgement</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>communication style conveying genuineness</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>A communication involving the expressed recognition of what another has expressed.</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
+          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr"/>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>sincerity</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:044021</t>
+          <t>BCIO:044112</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -3716,65 +3795,74 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>communication acknowledging difficulties</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>non-judgmental communication style</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
+          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr"/>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:044071</t>
+          <t>BCIO:044109</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>reflective communication</t>
-        </is>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>legitimising communication style</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
+          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr"/>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>validating emotions</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:044076</t>
+          <t>BCIO:044121</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -3782,36 +3870,32 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>re-evaluation prompting reflective communication</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>theatrical communication style</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>"amplified reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P98" t="inlineStr"/>
+          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:044072</t>
+          <t>BCIO:044105</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -3819,36 +3903,32 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>summarising reflective communication</t>
-        </is>
-      </c>
+      <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>impatient communication style</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>"summarising reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr"/>
+          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:044073</t>
+          <t>BCIO:044113</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
@@ -3856,36 +3936,36 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>double-sided reflective communication</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>patient communication style</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>"double-sided reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr"/>
+          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>"willing to listen"</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:044075</t>
+          <t>BCIO:044116</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -3893,36 +3973,36 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>emotion-emphasising reflective communication</t>
-        </is>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>relaxed communication style</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>"reflection of feeling" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr"/>
+          <t>A communication style characterised by a lack of tension or anxiety.</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>calm communication style</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:044074</t>
+          <t>BCIO:050391</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -3930,274 +4010,234 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>metaphor-using reflective communication</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>non-responsive communication style</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>"metaphorical reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P102" t="inlineStr"/>
+          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:044028</t>
+          <t>BCIO:044123</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>communication encouraging discussion</t>
-        </is>
-      </c>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>warm communication style</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
+          <t>A communication style which demonstrates human interest and caring.</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr"/>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>Contrasts with a more one-way, didactic style</t>
+          <t>friendly communication style</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:044036</t>
+          <t>BCIO:044115</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
-        </is>
-      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>polite communication style</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
+          <t>A communication style characterised by courtesy.</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr"/>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr">
-        <is>
-          <t>From Motivational Interviewing</t>
-        </is>
-      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:044069</t>
+          <t>BCIO:044111</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>offering reassurance</t>
-        </is>
-      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>non-confrontational communication style</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr"/>
+          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr"/>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>made reassuring statements</t>
-        </is>
-      </c>
-      <c r="Q105" t="inlineStr">
-        <is>
-          <t>based on Roter Interactional Analysis System</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:044018</t>
+          <t>BCIO:044107</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>branded communication</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>intellectual communication style</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>use of branding; brand identity</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Change for Life, Time to Change, NHS Smokefree</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:044022</t>
+          <t>BCIO:044104</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>communication adding intensity to another's views</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>formal communication style</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>"overshooting" in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr"/>
+          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:044030</t>
+          <t>BCIO:044079</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>exploring communication</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>active participation encouraging communication style</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
+          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr"/>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>eliciting or seeking information</t>
-        </is>
-      </c>
-      <c r="Q108" t="inlineStr">
-        <is>
-          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:050383</t>
+          <t>BCIO:044119</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -4205,36 +4245,40 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about a topic</t>
-        </is>
-      </c>
+      <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>semi-structured communication style</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to a matter.</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
+          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr"/>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Elicit concerns, problems and reactions</t>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>organised communication style</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:050387</t>
+          <t>BCIO:044083</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4242,37 +4286,41 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about an experience</t>
-        </is>
-      </c>
+      <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>attentive communication style</t>
+        </is>
+      </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about an experience.</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr"/>
+          <t>A communication style characterised by purposeful consideration of another's statements.</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr"/>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
-        </is>
-      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>"listened carefully to what you had to say"</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:050386</t>
+          <t>BCIO:044122</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -4280,36 +4328,32 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about a topic</t>
-        </is>
-      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>verbally dominant communication style</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about a matter.</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr"/>
+          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr"/>
-      <c r="O111" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>clarifying what someone has said</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:050385</t>
+          <t>BCIO:044131</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -4317,290 +4361,276 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about an experience</t>
-        </is>
-      </c>
+      <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>anxious communication style</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to an experience.</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr"/>
+          <t>A communication style characterised by nervousness or unease.</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr"/>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
-        </is>
-      </c>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:044058</t>
+          <t>BCIO:044094</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>communication using rational arguments</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>communication style conveying support for change</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr"/>
+          <t>A communication style which imparts one's belief that the recipient can change.</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr"/>
-      <c r="O113" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:044029</t>
+          <t>BCIO:050392</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>communication evoking another's ideas about change</t>
-        </is>
-      </c>
+      <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>rushed communication style</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>evoking change talk in motivational interviewing</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P114" t="inlineStr"/>
+          <t>A communication style conveying information in a hurried way.</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:044048</t>
+          <t>BCIO:050380</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>communication using deliberate pauses</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>aggressive communication style</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr"/>
+          <t>A communication style characterised by aggression.</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr"/>
-      <c r="O115" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>staying silent (where this is intended to give others the chance to speak)</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:044035</t>
+          <t>BCIO:050390</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>communication inviting reactions to content presented</t>
-        </is>
-      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>humorous communication style</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>A communication seeking information about a person's responses to the  content presented.</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>asking for opinions</t>
-        </is>
-      </c>
-      <c r="O116" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P116" t="inlineStr"/>
+          <t>A communication style intended to amuse.</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:044070</t>
+          <t>BCIO:044114</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>paraphrasing</t>
-        </is>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>persuasive communication style</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>A communication in which one participant summarises what the other said.</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr"/>
+          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr"/>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr">
-        <is>
-          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
-        </is>
-      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:044040</t>
+          <t>BCIO:044084</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>communication involving elaboration of arguments</t>
-        </is>
-      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>autonomy-supportive communication style</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr"/>
+          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>from Self-Determination Theory interventions.</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr"/>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>needs-supportive communication style</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:044050</t>
+          <t>BCIO:044098</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>communication using particular language</t>
-        </is>
-      </c>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>didactic communication style</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>A communication using certain vocabulary or phraseology.</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr"/>
+          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr"/>
-      <c r="O119" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>gave a short lecture, conference presentation</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:044052</t>
+          <t>BCIO:044086</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -4608,32 +4638,32 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>communication using non-pressurising language</t>
-        </is>
-      </c>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>cold communication style</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr"/>
+          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr"/>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:044055</t>
+          <t>BCIO:044099</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -4641,32 +4671,41 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>communication avoiding offensive language</t>
-        </is>
-      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>directive communication style</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
+          <t>A communication style intended to play an active role in another person's decision making.</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Note that this class is different from direct communication style</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr"/>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:044051</t>
+          <t>BCIO:044097</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4674,32 +4713,32 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>communication using neutral language</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>conversational communication style</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr"/>
+          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr"/>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:044053</t>
+          <t>BCIO:044120</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4707,32 +4746,41 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>communication using slang</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>structured communication style</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>A communication using informal language shared by members of a particular community.</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
+          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr"/>
-      <c r="O123" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>standardised</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:044054</t>
+          <t>BCIO:044102</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4740,36 +4788,32 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>communication using specialist language</t>
-        </is>
-      </c>
+      <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr"/>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>engaging communication style</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>using jargon</t>
-        </is>
-      </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P124" t="inlineStr"/>
+          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:044056</t>
+          <t>BCIO:044118</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4777,103 +4821,107 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>communication using selected words from a second language</t>
-        </is>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>responsive communication style</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr"/>
+          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr"/>
-      <c r="O125" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:044026</t>
+          <t>BCIO:044091</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>communication checking for others' understanding</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>communication style conveying hopefulness</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
-        </is>
-      </c>
-      <c r="L126" t="inlineStr"/>
+          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr"/>
-      <c r="O126" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>optimism, positivity</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:044019</t>
+          <t>BCIO:044095</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>discussion</t>
-        </is>
-      </c>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>communication style demonstrating positive regard</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr"/>
+          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr"/>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr">
-        <is>
-          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
-        </is>
-      </c>
+      <c r="N127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:044020</t>
+          <t>BCIO:044101</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -4881,640 +4929,612 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>classroom-style discussion</t>
-        </is>
-      </c>
+      <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>empathic communication style</t>
+        </is>
+      </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
-        </is>
-      </c>
-      <c r="L128" t="inlineStr"/>
+          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr"/>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>sensitivity, compassion</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:044017</t>
+          <t>BCIO:044108</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>banter</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>interactive communication style</t>
+        </is>
+      </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
-        </is>
-      </c>
-      <c r="L129" t="inlineStr"/>
+          <t>A communication style characterised by being responsive to the recipient's activity.</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr"/>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr">
-        <is>
-          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
-        </is>
-      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>interactive presentation</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:044064</t>
+          <t>BCIO:044110</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>narrative communication</t>
-        </is>
-      </c>
+      <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>non-defensive communication style</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
-        </is>
-      </c>
-      <c r="L130" t="inlineStr"/>
+          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr"/>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:044010</t>
+          <t>BCIO:044087</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>affirming communication</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>communication style conveying acceptance</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr"/>
+          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr"/>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Making explicit statements of partnership or support; Shows approval;</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:044023</t>
+          <t>BCIO:050381</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>communication asking permission to provide information and advice</t>
-        </is>
-      </c>
+      <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>angry communication style</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
-        </is>
-      </c>
-      <c r="L132" t="inlineStr"/>
+          <t>A communication style characterised by anger.</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr"/>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:044060</t>
+          <t>BCIO:044000</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>guiding communication</t>
-        </is>
-      </c>
+      <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>behaviour change intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr"/>
+          <t>A communication style that is an attribute of a BCI content communication process.</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr"/>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:044024</t>
+          <t>BCIO:044130</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>communication avoiding argumentation</t>
-        </is>
-      </c>
+      <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>readability</t>
+        </is>
+      </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr"/>
+          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr"/>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P134" t="inlineStr"/>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:044047</t>
+          <t>BCIO:044129</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>communication using commands</t>
-        </is>
-      </c>
+      <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>object layout</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>communication using imperatives</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr"/>
+          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:044041</t>
+          <t>BCIO:044125</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>communication offering choice</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>tone of voice</t>
+        </is>
+      </c>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>A communication involving the initiator offering a range of options to the recipient.</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr"/>
+          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr"/>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:044043</t>
+          <t>BCIO:044128</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>communication using a particular form of address</t>
-        </is>
-      </c>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>source visual style</t>
+        </is>
+      </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr"/>
+          <t>An attribute of an intervention person source concerning how they appear to others.</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>may be purposefully chosen to convey certain attributes of the source</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr"/>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr">
-        <is>
-          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
-        </is>
-      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:044046</t>
+          <t>BCIO:050552</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>communication channel</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>communication using preferred form of address</t>
-        </is>
-      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
-        </is>
-      </c>
-      <c r="L138" t="inlineStr"/>
+          <t>A &lt;process&gt; by which a communication is delivered.</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr"/>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>BCIO:044044</t>
+          <t>OBI:0000011</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>planned process</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>communication using formal address</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr"/>
+          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:044045</t>
+          <t>BCIO:045000</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>communication using informal address</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>intervention delivery</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr"/>
+          <t>A planned process by which intervention content is delivered.</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr"/>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:044027</t>
+          <t>BCIO:044007</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>communication checking for own understanding</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>participant-led intervention delivery</t>
+        </is>
+      </c>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr"/>
+          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr"/>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>clarifying what another has said</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:044039</t>
+          <t>BCIO:008000</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>communication involving confirmatory rephrasing</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>behaviour change intervention delivery</t>
+        </is>
+      </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>"coming alongside" in Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr"/>
+          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:044124</t>
+          <t>BCIO:044008</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>relationship building</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>source-led intervention delivery</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr"/>
+          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr"/>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
-        </is>
-      </c>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BCIO:044062</t>
+          <t>BCIO:044006</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>communication avoiding interrupting</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>person-centred intervention delivery</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
-        </is>
-      </c>
-      <c r="L144" t="inlineStr"/>
+          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr"/>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>BCIO:044077</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>script-based communication</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr">
-        <is>
-          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:044078</t>
+          <t>BCIO:036000</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -5523,7 +5543,7 @@
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>shifting focus of communication</t>
+          <t>individual human behaviour</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -5532,55 +5552,39 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr"/>
+          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:044012</t>
+          <t>BCIO:050441</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>asking questions</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>socially-related behaviour</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>A communication in which some participant requests information from another participant.</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr"/>
+          <t>An individual human behaviour that relates to the social environment.</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:044014</t>
+          <t>BCIO:036025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
@@ -5588,32 +5592,32 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>asking focused questions</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>inter-personal behaviour</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr"/>
+          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr"/>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:044013</t>
+          <t>BCIO:036034</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -5621,32 +5625,32 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>asking closed-ended questions</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>human communication behaviour</t>
+        </is>
+      </c>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>Asking questions that can only be answered with a limited set of responses.</t>
-        </is>
-      </c>
-      <c r="L149" t="inlineStr"/>
+          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr"/>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BCIO:044015</t>
+          <t>BCIO:050237</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -5654,36 +5658,32 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>asking leading questions</t>
-        </is>
-      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>linguistic communication behaviour</t>
+        </is>
+      </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
-        </is>
-      </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>asking directive questions</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr"/>
+          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BCIO:044016</t>
+          <t>BCIO:050457</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5693,7 +5693,7 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>asking open-ended questions</t>
+          <t>expressive behaviour</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -5701,22 +5701,22 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr"/>
+          <t>An individual human behaviour that conveys a thought or feeling.</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr"/>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BCIO:050382</t>
+          <t>BCIO:050374</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -5724,27 +5724,27 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>asking clarifying questions</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>laughing</t>
+        </is>
+      </c>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>Asking questions in order to better understand an issue.</t>
-        </is>
-      </c>
-      <c r="L152" t="inlineStr"/>
+          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr"/>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5774,14 +5774,14 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
       <c r="D154" t="inlineStr">
         <is>
-          <t>independent continuant</t>
+          <t>generically dependent continuant</t>
         </is>
       </c>
       <c r="E154" t="inlineStr"/>
@@ -5792,14 +5792,14 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -5807,7 +5807,7 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>material entity</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
@@ -5817,14 +5817,14 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+          <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OGMS:0000087</t>
+          <t>BCIO:050555</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -5833,7 +5833,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>extended organism</t>
+          <t>communication message</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -5842,67 +5842,67 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
-        </is>
-      </c>
+          <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr"/>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>person</t>
-        </is>
-      </c>
+      <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BCIO:050553</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>communication recipient</t>
-        </is>
-      </c>
+      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; who receives a communication.</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P158" t="inlineStr"/>
+          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5928,97 +5928,97 @@
           <t>A &lt;material entity&gt; that originates a communication.</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr"/>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>OGMS:0000087</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>extended organism</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
+          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>MF:0000016</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>human being</t>
+        </is>
+      </c>
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:050555</t>
+          <t>BCIO:050553</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>communication message</t>
-        </is>
-      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>communication recipient</t>
+        </is>
+      </c>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr"/>
+          <t>A &lt;person&gt; who receives a communication.</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr"/>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="P162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/StyleOfDelivery/BCIO-style-hierarchy.xlsx
+++ b/StyleOfDelivery/BCIO-style-hierarchy.xlsx
@@ -447,27 +447,27 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>synonyms</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>crossreference</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>examples</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>synonyms</t>
         </is>
       </c>
     </row>
@@ -524,13 +524,13 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BFO:0000003</t>
+          <t>BFO:0000002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>occurrent</t>
+          <t>continuant</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -542,21 +542,21 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
+          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BFO:0000015</t>
+          <t>BFO:0000031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>generically dependent continuant</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -567,14 +567,14 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BCIO:050384</t>
+          <t>IAO:0000030</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -582,7 +582,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>communication</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -592,27 +592,14 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>A process involving the transmission of information between two or more participants.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
+          <t>A generically dependent continuant that is about some thing.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:044069</t>
+          <t>BCIO:050555</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -621,7 +608,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>offering reassurance</t>
+          <t>communication message</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -630,105 +617,72 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>based on Roter Interactional Analysis System</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>made reassuring statements</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:044039</t>
+          <t>BFO:0000004</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>independent continuant</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>communication involving confirmatory rephrasing</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>"coming alongside" in Motivational Interviewing</t>
+          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:044035</t>
+          <t>BFO:0000040</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>communication inviting reactions to content presented</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>A communication seeking information about a person's responses to the  content presented.</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>asking for opinions</t>
+          <t>An &lt;independent continuant&gt; that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BCIO:044011</t>
+          <t>BCIO:050554</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -737,7 +691,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>agenda-sharing communication</t>
+          <t>communication source</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -746,26 +700,22 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>A &lt;material entity&gt; that originates a communication.</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>agenda mapping</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:044065</t>
+          <t>OGMS:0000087</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -774,7 +724,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>negotiation</t>
+          <t>extended organism</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -783,60 +733,39 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:044043</t>
+          <t>MF:0000016</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>communication using a particular form of address</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>person</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>An extended organism that is a member of the species Homo sapiens.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:044045</t>
+          <t>BCIO:050553</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -844,135 +773,107 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>communication using informal address</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>communication recipient</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>A &lt;person&gt; who receives a communication.</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:044046</t>
+          <t>BFO:0000003</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>occurrent</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>communication using preferred form of address</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>An entity that has temporal parts and that happens, unfolds or develops through time.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:044044</t>
+          <t>BFO:0000015</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>communication using formal address</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:044009</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>active listening</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>process profile</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:044027</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -981,7 +882,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>communication checking for own understanding</t>
+          <t>process attribute</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -990,64 +891,52 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>clarifying what another has said</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+          <t>A process profile that is an attribute of a process.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:044019</t>
+          <t>BCIO:044003</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>discussion</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>communication process attribute</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
+          <t>An attribute of a communication process.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:044020</t>
+          <t>BCIO:044129</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1055,185 +944,191 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>classroom-style discussion</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>object layout</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:044010</t>
+          <t>BCIO:044128</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>affirming communication</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>source visual style</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Making explicit statements of partnership or support; Shows approval;</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+          <t>An attribute of an intervention person source concerning how they appear to others.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>may be purposefully chosen to convey certain attributes of the source</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:044049</t>
+          <t>BCIO:044125</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>communication using interjections to signal attentiveness</t>
-        </is>
-      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>tone of voice</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Words like "interesting", "yeah"," mmhmm"</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
-        </is>
-      </c>
+          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:044047</t>
+          <t>BCIO:044004</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>communication using commands</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>communication style</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>communication using imperatives</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:044050</t>
+          <t>BCIO:044083</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>communication using particular language</t>
-        </is>
-      </c>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>attentive communication style</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>A communication using certain vocabulary or phraseology.</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
+          <t>A communication style characterised by purposeful consideration of another's statements.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>"listened carefully to what you had to say"</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:044055</t>
+          <t>BCIO:044005</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1241,32 +1136,37 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>communication avoiding offensive language</t>
-        </is>
-      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
+          <t>A communication style that is an attribute of an intervention content communication process.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:044052</t>
+          <t>BCIO:044099</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1274,32 +1174,41 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>communication using non-pressurising language</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>directive communication style</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
+          <t>A communication style intended to play an active role in another person's decision making.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Note that this class is different from direct communication style</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:044051</t>
+          <t>BCIO:044106</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1307,32 +1216,37 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>communication using neutral language</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>informal communication style</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:044053</t>
+          <t>BCIO:044089</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1340,32 +1254,32 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>communication using slang</t>
-        </is>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>communication style conveying concern</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>A communication using informal language shared by members of a particular community.</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
+          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:044054</t>
+          <t>BCIO:044100</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1373,36 +1287,41 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>communication using specialist language</t>
-        </is>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>easily comprehended communication style</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
+          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>This can involve using plain and simple language</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>using jargon</t>
+          <t>using non-technical language, using clear language, avoiding jargon</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:044056</t>
+          <t>BCIO:044119</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1410,139 +1329,139 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>communication using selected words from a second language</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>semi-structured communication style</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr"/>
+          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>organised communication style</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:044124</t>
+          <t>BCIO:044085</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>relationship building</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>collaborative communication style</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:044042</t>
+          <t>BCIO:044087</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>communication understating intensity of person's views</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>communication style conveying acceptance</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
+          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>"undershooting" in motivational interviewing</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:044012</t>
+          <t>BCIO:044121</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>asking questions</t>
-        </is>
-      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>theatrical communication style</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A communication in which some participant requests information from another participant.</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
+          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:050382</t>
+          <t>BCIO:044107</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1550,32 +1469,32 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>asking clarifying questions</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>intellectual communication style</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Asking questions in order to better understand an issue.</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
+          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:044014</t>
+          <t>BCIO:050380</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1583,32 +1502,32 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>asking focused questions</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>aggressive communication style</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+          <t>A communication style characterised by aggression.</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:044015</t>
+          <t>BCIO:044110</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1616,36 +1535,32 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>asking leading questions</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>non-defensive communication style</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
+          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>asking directive questions</t>
-        </is>
-      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:044016</t>
+          <t>BCIO:044116</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1653,32 +1568,36 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>asking open-ended questions</t>
-        </is>
-      </c>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>relaxed communication style</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by a lack of tension or anxiety.</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>calm communication style</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:044013</t>
+          <t>BCIO:044117</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1686,112 +1605,107 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>asking closed-ended questions</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>respectful communication style</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Asking questions that can only be answered with a limited set of responses.</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
+          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
+        </is>
+      </c>
       <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>"acknowledging the victim's feelings"</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:044028</t>
+          <t>BCIO:044112</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>communication encouraging discussion</t>
-        </is>
-      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>non-judgmental communication style</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Contrasts with a more one-way, didactic style</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
+          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:044030</t>
+          <t>BCIO:044104</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>exploring communication</t>
-        </is>
-      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>formal communication style</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>eliciting or seeking information</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:050385</t>
+          <t>BCIO:044108</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1799,37 +1713,36 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about an experience</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>interactive communication style</t>
+        </is>
+      </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to an experience.</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
+          <t>A communication style characterised by being responsive to the recipient's activity.</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>interactive presentation</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:050387</t>
+          <t>BCIO:044114</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1837,37 +1750,32 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about an experience</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>persuasive communication style</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about an experience.</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>An experience can be any situation or state a person encounters or undergoes</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
+          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:050386</t>
+          <t>BCIO:044111</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1875,36 +1783,32 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>communication exploring a person's thoughts about a topic</t>
-        </is>
-      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>non-confrontational communication style</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>An exploring communication focused on what a person thinks about a matter.</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>clarifying what someone has said</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:050383</t>
+          <t>BCIO:044102</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1912,317 +1816,305 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>communication exploring a person's feelings about a topic</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>engaging communication style</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>An exploring communication focused on a person's affective responses to a matter.</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Elicit concerns, problems and reactions</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:044024</t>
+          <t>BCIO:044079</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>communication avoiding argumentation</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>active participation encouraging communication style</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
+          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:044060</t>
+          <t>BCIO:044091</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>guiding communication</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>communication style conveying hopefulness</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
+          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>optimism, positivity</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:044077</t>
+          <t>BCIO:050391</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>script-based communication</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>non-responsive communication style</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
+          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
+        </is>
+      </c>
       <c r="N46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:044059</t>
+          <t>BCIO:044094</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>emotionally expressive communication</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>communication style conveying support for change</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
+          <t>A communication style which imparts one's belief that the recipient can change.</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:044040</t>
+          <t>BCIO:044122</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>communication involving elaboration of arguments</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>verbally dominant communication style</t>
+        </is>
+      </c>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
+          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:044018</t>
+          <t>BCIO:050389</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>branded communication</t>
-        </is>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>direct communication style</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Change for Life, Time to Change, NHS Smokefree</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>use of branding; brand identity</t>
-        </is>
-      </c>
+          <t>A communication style characterised by the explicit presentation of information.</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Note that this class is different from directive communication style</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:044026</t>
+          <t>BCIO:044105</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>communication checking for others' understanding</t>
-        </is>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>impatient communication style</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
+          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:044071</t>
+          <t>BCIO:044131</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>reflective communication</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>anxious communication style</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
+          <t>A communication style characterised by nervousness or unease.</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:044076</t>
+          <t>BCIO:044084</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2230,36 +2122,41 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>re-evaluation prompting reflective communication</t>
-        </is>
-      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>autonomy-supportive communication style</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>"amplified reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
+          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>from Self-Determination Theory interventions.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>needs-supportive communication style</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:044074</t>
+          <t>BCIO:044086</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2267,36 +2164,32 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>metaphor-using reflective communication</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>cold communication style</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
+          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>"metaphorical reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:044075</t>
+          <t>BCIO:044098</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2304,36 +2197,36 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>emotion-emphasising reflective communication</t>
-        </is>
-      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>didactic communication style</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>"reflection of feeling" in Motivational Interviewing</t>
+          <t>gave a short lecture, conference presentation</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:044073</t>
+          <t>BCIO:044095</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2341,36 +2234,32 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>double-sided reflective communication</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>communication style demonstrating positive regard</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
+          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>"double-sided reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:044072</t>
+          <t>BCIO:044118</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2378,143 +2267,150 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>summarising reflective communication</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>responsive communication style</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
+          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>"summarising reflection" in Motivational Interviewing</t>
-        </is>
-      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:044022</t>
+          <t>BCIO:044120</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>communication adding intensity to another's views</t>
-        </is>
-      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>structured communication style</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>"overshooting" in motivational interviewing</t>
-        </is>
-      </c>
+          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>standardised</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:044029</t>
+          <t>BCIO:050381</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>communication evoking another's ideas about change</t>
-        </is>
-      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>angry communication style</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr"/>
+          <t>A communication style characterised by anger.</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>evoking change talk in motivational interviewing</t>
-        </is>
-      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:050388</t>
+          <t>BCIO:044000</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>communication showing acknowledgement</t>
-        </is>
-      </c>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>behaviour change intervention style of delivery</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>A communication involving the expressed recognition of what another has expressed.</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr"/>
+          <t>A communication style that is an attribute of a BCI content communication process.</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:044021</t>
+          <t>BCIO:044082</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2522,395 +2418,391 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>communication acknowledging difficulties</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>articulate communication style</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>fluent</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:044048</t>
+          <t>BCIO:044103</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>communication using deliberate pauses</t>
-        </is>
-      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>entertaining communication style</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr"/>
+          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>staying silent (where this is intended to give others the chance to speak)</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>fun</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:044070</t>
+          <t>BCIO:044101</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>paraphrasing</t>
-        </is>
-      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>empathic communication style</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>A communication in which one participant summarises what the other said.</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>sensitivity, compassion</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:044064</t>
+          <t>BCIO:044109</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>narrative communication</t>
-        </is>
-      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>legitimising communication style</t>
+        </is>
+      </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>validating emotions</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:044061</t>
+          <t>BCIO:044115</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>interrupting</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>polite communication style</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>A communication in which one person interjects before another has finished making their point.</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr"/>
+          <t>A communication style characterised by courtesy.</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:044023</t>
+          <t>BCIO:044092</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>communication asking permission to provide information and advice</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>communication style conveying perceived superiority</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:044034</t>
+          <t>BCIO:050392</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>communication highlighting a contradiction</t>
-        </is>
-      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>rushed communication style</t>
+        </is>
+      </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr"/>
+          <t>A communication style conveying information in a hurried way.</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:044036</t>
+          <t>BCIO:044113</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>patient communication style</t>
+        </is>
+      </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>From Motivational Interviewing</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr"/>
+          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>"willing to listen"</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:044017</t>
+          <t>BCIO:050390</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>banter</t>
-        </is>
-      </c>
+      <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>humorous communication style</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr">
         <is>
-          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr"/>
+          <t>A communication style intended to amuse.</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:044078</t>
+          <t>BCIO:044123</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>shifting focus of communication</t>
-        </is>
-      </c>
+      <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>warm communication style</t>
+        </is>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr">
         <is>
-          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication style which demonstrates human interest and caring.</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>friendly communication style</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:044037</t>
+          <t>BCIO:044097</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>communication involving agreement</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>conversational communication style</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>A communication in which one participant concurs with the views stated by another.</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr"/>
+          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:044038</t>
+          <t>BCIO:044090</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2918,173 +2810,176 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>communication involving agreement followed by highlighting incongruent aspects</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>communication style conveying genuineness</t>
+        </is>
+      </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
-          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>"agreement with a twist" in motivational interviewing</t>
-        </is>
-      </c>
+          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>sincerity</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:044041</t>
+          <t>BCIO:044081</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>communication offering choice</t>
-        </is>
-      </c>
+      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>aloof communication style</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>A communication involving the initiator offering a range of options to the recipient.</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr"/>
+          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:044058</t>
+          <t>BCIO:044096</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>communication using rational arguments</t>
-        </is>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>controlling communication style</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr"/>
+          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:044062</t>
+          <t>BCIO:044127</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>communication avoiding interrupting</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>object visual style</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr"/>
+          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:044001</t>
+          <t>BCIO:044130</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>intervention content communication process</t>
-        </is>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>readability</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
-          <t>A communication that transmits the content of an intervention</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr"/>
+          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:044002</t>
+          <t>BCIO:044126</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3092,37 +2987,32 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>behaviour change intervention content communication process</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>oral communication pace</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>An intervention content communication process that is about behaviour change intervention content</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>OGMS:0000060</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -3130,7 +3020,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>process profile</t>
+          <t>bodily process</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -3140,14 +3030,14 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
+          <t>A process in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:036000</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -3156,7 +3046,7 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>process attribute</t>
+          <t>individual human behaviour</t>
         </is>
       </c>
       <c r="G78" t="inlineStr"/>
@@ -3165,14 +3055,14 @@
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
+          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:044003</t>
+          <t>BCIO:050441</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -3182,7 +3072,7 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>communication process attribute</t>
+          <t>socially-related behaviour</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -3190,27 +3080,14 @@
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>An attribute of a communication process.</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Communication processes can have a variety of attributes, such as their speed, how they are delivered, what language they take place in and the tone of voice in which they occur.  All these types of attributes and more are captured by "communication process attribute"</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr"/>
+          <t>An individual human behaviour that relates to the social environment.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:044126</t>
+          <t>BCIO:036025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3221,29 +3098,29 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>oral communication pace</t>
+          <t>inter-personal behaviour</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the speed with which an individual speaks.</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr"/>
+          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:044127</t>
+          <t>BCIO:036034</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3254,33 +3131,29 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>object visual style</t>
+          <t>human communication behaviour</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>An attribute of an object used in a communication process, concerning how information sensed with the eyes is presented, which may include colours/fonts/images/spacing/sizing.</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>colour scheme chosen for a website, style of images used for a booklet, brightly coloured reminder stickers</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BCIO:044004</t>
+          <t>BCIO:050237</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
@@ -3289,31 +3162,31 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>communication style</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>linguistic communication behaviour</t>
+        </is>
+      </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr">
         <is>
-          <t>A particular manner of communicating aimed at inducing or avoiding certain kinds of responses in others, or demonstrating certain characteristics of the initiator.</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr"/>
+          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BCIO:044100</t>
+          <t>BCIO:050457</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -3321,41 +3194,32 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>expressive behaviour</t>
+        </is>
+      </c>
       <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>easily comprehended communication style</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr">
         <is>
-          <t>A communication style characterised by using language in a manner intended to be easily understandable to a recipient.</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>This can involve using plain and simple language</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>using non-technical language, using clear language, avoiding jargon</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>An individual human behaviour that conveys a thought or feeling.</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>BCIO:044081</t>
+          <t>BCIO:050374</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -3364,135 +3228,144 @@
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>aloof communication style</t>
-        </is>
-      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>laughing</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of empathy or compassion for the recipient.</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr"/>
+          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>BCIO:044005</t>
+          <t>BCIO:050552</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>communication channel</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of an intervention content communication process.</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of an intervention content communication process, then it qualifies as an intervention style of delivery</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr"/>
+          <t>A &lt;process&gt; by which a communication is delivered.</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BCIO:044096</t>
+          <t>BCIO:050384</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>controlling communication style</t>
-        </is>
-      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>A communication style which directly instructs the adoption of certain beliefs, theories or lines of action.</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr"/>
+          <t>A process involving the transmission of information between two or more participants.</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>The participants in the communication process can be of a variety of types, e.g. a human talking to an automated chatbot system, two computer systems exchanging information, a person talking to a pet animal etc.</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BCIO:044092</t>
+          <t>BCIO:044030</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>exploring communication</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>communication style conveying perceived superiority</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling that the instigator believes themselves to be higher in status than the recipient.</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr"/>
+          <t>A communication to better understand what a person thinks or feels about a topic or an experience.</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>This can include asking questions or prompting elaboration e.g 'Tell me more about that'</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>eliciting or seeking information</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>BCIO:044103</t>
+          <t>BCIO:050386</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -3500,36 +3373,36 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about a topic</t>
+        </is>
+      </c>
       <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>entertaining communication style</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr">
         <is>
-          <t>A communication style intended to be amusing or enjoyable for the recipient.</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr"/>
+          <t>An exploring communication focused on what a person thinks about a matter.</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>fun</t>
+          <t>clarifying what someone has said</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BCIO:044082</t>
+          <t>BCIO:050385</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -3537,36 +3410,37 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about an experience</t>
+        </is>
+      </c>
       <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>articulate communication style</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator fluently using language to express ideas.</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr"/>
+          <t>An exploring communication focused on a person's affective responses to an experience.</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>fluent</t>
-        </is>
-      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BCIO:044089</t>
+          <t>BCIO:050383</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -3574,32 +3448,36 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>communication exploring a person's feelings about a topic</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>communication style conveying concern</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
-          <t>A communication style demonstrating one perceives an unwanted circumstance for the recipient.</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr"/>
+          <t>An exploring communication focused on a person's affective responses to a matter.</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Elicit concerns, problems and reactions</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BCIO:044106</t>
+          <t>BCIO:050387</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -3607,885 +3485,903 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>communication exploring a person's thoughts about an experience</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>informal communication style</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of casual or colloquial language rather than formal language.</t>
+          <t>An exploring communication focused on what a person thinks about an experience.</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>"Colloquial" language is language that is typically used in ordinary conversation rather than in formal communication</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr"/>
+          <t>An experience can be any situation or state a person encounters or undergoes</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>BCIO:044085</t>
+          <t>BCIO:044011</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>agenda-sharing communication</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>collaborative communication style</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
-          <t>A communication style characterised by a sense of the initiator and recipient working together, the initiator showing sensitivity to the others' needs, in order to obtain an outcome desired by all.</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication in which the initiator and one or more activity participants work together to determine a focus for the activity to be undertaken.</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>agenda mapping</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BCIO:044117</t>
+          <t>BCIO:044039</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>communication involving confirmatory rephrasing</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>respectful communication style</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>A communication style suggesting an understanding of and regard for the feelings, wishes, or rights of others.</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>This class involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says.  In contrast, responsive communication style is adapting the response as a result of how another person is communicating.</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
+          <t>A communication involving the initiator rephrasing what a recipient says in a manner intended to confirm understanding of the recipient's situation rather than confront.</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>"acknowledging the victim's feelings"</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>"coming alongside" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>BCIO:050389</t>
+          <t>BCIO:044027</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>communication checking for own understanding</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>direct communication style</t>
-        </is>
-      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>A communication style characterised by the explicit presentation of information.</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Note that this class is different from directive communication style</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr"/>
+          <t>A communication in which the instigator asks questions to determine if they have correctly comprehended the information presented by another.</t>
+        </is>
+      </c>
       <c r="N94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>clarifying what another has said</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BCIO:044090</t>
+          <t>BCIO:044062</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>communication avoiding interrupting</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr"/>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>communication style conveying genuineness</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>A communication style which suggests one is acting in line with one's true values and beliefs.</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr"/>
+          <t>A communication in which at least one participant endeavours to not interject before another participant has finished making their point.</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>sincerity</t>
-        </is>
-      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BCIO:044112</t>
+          <t>BCIO:044065</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>negotiation</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr"/>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>non-judgmental communication style</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>A communication style that demonstrates that one is not assigning a positive or negative valence to another's views or behaviours.</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr"/>
+          <t>A communication involving goal-oriented collaboration to arrive at an agreement or compromise on a matter of importance to the individuals involved.</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>BCIO:044109</t>
+          <t>BCIO:044061</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>interrupting</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>legitimising communication style</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>A communication style characterised by making a person feel that their perspective or emotions are legitimate.</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>This entails a deliberate strategy to make the person feel their perspective is legitimate</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr"/>
+          <t>A communication in which one person interjects before another has finished making their point.</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q97" t="inlineStr">
-        <is>
-          <t>validating emotions</t>
-        </is>
-      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BCIO:044121</t>
+          <t>BCIO:044064</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>narrative communication</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>theatrical communication style</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr">
         <is>
-          <t>A communication style similar to that used for dramatic performance or the theatre.</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr"/>
+          <t>A communication describing the particulars of a person's life or a course of events in the style of telling a story.</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BCIO:044105</t>
+          <t>BCIO:044023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>communication asking permission to provide information and advice</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr"/>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>impatient communication style</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>A communication style conveying feelings of annoyance at time taken to understand or complete a process.</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr"/>
+          <t>A communication which involves asking for approval before sharing knowledge and giving guidance.</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Educate using “ask-tell-ask” rather than “tell-ask-tell”</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>BCIO:044113</t>
+          <t>BCIO:044022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>communication adding intensity to another's views</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>patient communication style</t>
-        </is>
-      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>A communication style conveying willingness to take time to understand or complete a process.</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr"/>
+          <t>A communication using statements that add intensity to the content or emotion expressed by another person.</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>"willing to listen"</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>"overshooting" in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>BCIO:044116</t>
+          <t>BCIO:044048</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>communication using deliberate pauses</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr"/>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>relaxed communication style</t>
-        </is>
-      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>A communication style characterised by a lack of tension or anxiety.</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr"/>
+          <t>A communication in which the speaker purposely leaves gaps between or after their speech utterances.</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Pauses may be deliberately left to provide opportunities for others to speak or reflect, or to demonstrate non-directiveness.</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>calm communication style</t>
+          <t>staying silent (where this is intended to give others the chance to speak)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>BCIO:050391</t>
+          <t>BCIO:044034</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>communication highlighting a contradiction</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr"/>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>non-responsive communication style</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>A communication style characterised by not adapting to the views and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr"/>
+          <t>A communication pointing out a situation in which actions or propositions are inconsistent with each other.</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>The contradiction can be between two or more of a person's actions, or between a person's actions and beliefs, or between two or more beliefs a person holds</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>BCIO:044123</t>
+          <t>BCIO:044035</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>communication inviting reactions to content presented</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>warm communication style</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>A communication style which demonstrates human interest and caring.</t>
-        </is>
-      </c>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="P103" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q103" t="inlineStr">
-        <is>
-          <t>friendly communication style</t>
-        </is>
-      </c>
+          <t>A communication seeking information about a person's responses to the  content presented.</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>asking for opinions</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BCIO:044115</t>
+          <t>BCIO:044059</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>emotionally expressive communication</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr"/>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>polite communication style</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>A communication style characterised by courtesy.</t>
-        </is>
-      </c>
-      <c r="M104" t="inlineStr"/>
+          <t>A communication in a manner which clearly conveys the emotions of the initiator.</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>BCIO:044111</t>
+          <t>BCIO:044070</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>paraphrasing</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>non-confrontational communication style</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr">
         <is>
-          <t>A communication style characterised by being diplomatic and avoiding conflict.</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr"/>
+          <t>A communication in which one participant summarises what the other said.</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>This class is different to "communication involving confirmatory rephrasing" as this class is simply about summarising what another person said.</t>
+        </is>
+      </c>
       <c r="N105" t="inlineStr"/>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>BCIO:044107</t>
+          <t>BCIO:044058</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>communication using rational arguments</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr"/>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>intellectual communication style</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>A communication style characterised by an emphasis on reasoning and promoting objective understanding.</t>
-        </is>
-      </c>
-      <c r="M106" t="inlineStr"/>
+          <t>A communication that involves the use of declarative propositions based on what the communicator believes to be logical.</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>BCIO:044104</t>
+          <t>BCIO:044036</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>communication involving acceptance that recipients views may be different to the initiator's views</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>formal communication style</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>A communication style characterised by the use of traditional standards of correctness and etiquette and without casual, contracted, or colloquial forms of language.</t>
-        </is>
-      </c>
-      <c r="M107" t="inlineStr"/>
+          <t>A communication involving accepting that the recipient has different beliefs to the initiator and continuing with the planned activities while allowing both views to exist.</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>From Motivational Interviewing</t>
+        </is>
+      </c>
       <c r="N107" t="inlineStr"/>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BCIO:044079</t>
+          <t>BCIO:044042</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>communication understating intensity of person's views</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>active participation encouraging communication style</t>
-        </is>
-      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>A communication style marked by fostering the involvement of the recipient as an engaged actor in the activity to be undertaken rather than as a passive recipient.</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication using statements that diminish or understate the intensity of the content or emotion expressed by the other person.</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>"undershooting" in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BCIO:044119</t>
+          <t>BCIO:044010</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>affirming communication</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>semi-structured communication style</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having some constituent pre-planned parts but also being responsive to inputs.</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>Using talking points, using conversation guides, having a list of topics to cover</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication involving acknowledging another's strength or resilience in a given context or situation.</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>organised communication style</t>
+          <t>Making explicit statements of partnership or support; Shows approval;</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>BCIO:044083</t>
+          <t>BCIO:044040</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>communication involving elaboration of arguments</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>attentive communication style</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>A communication style characterised by purposeful consideration of another's statements.</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>This involves communicating in a manner that ensures the recipient knows that they are being heard</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>"listened carefully to what you had to say"</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication further developing a declarative statement that has been made  by making it clearer, more precise, bringing out its consequences or giving a concrete example.</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>BCIO:044122</t>
+          <t>BCIO:044026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>communication checking for others' understanding</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>verbally dominant communication style</t>
-        </is>
-      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>A communication style characterised by one participant having more control over a conversation than the other.</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr"/>
+          <t>A communication in which the instigator asks questions to determine if the recipient has comprehended information that has been presented.</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
-      <c r="P111" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BCIO:044131</t>
+          <t>BCIO:044018</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>branded communication</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr"/>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>anxious communication style</t>
-        </is>
-      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>A communication style characterised by nervousness or unease.</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q112" t="inlineStr"/>
+          <t>A communication using a consistent style of text or graphics to identify and distinguish a product, service or intervention from other products, services or interventions.</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>use of branding; brand identity</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Change for Life, Time to Change, NHS Smokefree</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BCIO:044094</t>
+          <t>BCIO:044077</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>script-based communication</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>communication style conveying support for change</t>
-        </is>
-      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>A communication style which imparts one's belief that the recipient can change.</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr"/>
+          <t>A communication which follows a pre-written sequence of instructions that are interpreted or carried out by a person or by a program.</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>This class involves tightly following a set of written instructions. It is different to structured communication style, which is a pre-planned style but not to the extent of using a written script.</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BCIO:050392</t>
+          <t>BCIO:044041</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>communication offering choice</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>rushed communication style</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr">
         <is>
-          <t>A communication style conveying information in a hurried way.</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr"/>
+          <t>A communication involving the initiator offering a range of options to the recipient.</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BCIO:050380</t>
+          <t>BCIO:044043</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>communication using a particular form of address</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>aggressive communication style</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>A communication style characterised by aggression.</t>
-        </is>
-      </c>
-      <c r="M115" t="inlineStr"/>
+          <t>A communication addressing a person using a certain name or title to refer to that person.</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>The child classes of this class are specific types of address, whereas this class is for a non-specific type of address.</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
-      <c r="P115" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BCIO:050390</t>
+          <t>BCIO:044045</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -4493,32 +4389,32 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>communication using informal address</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>humorous communication style</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>A communication style intended to amuse.</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr"/>
+          <t>A communication addressing a person using a casual or colloquial name or title to refer to that person.</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
-      <c r="P116" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>BCIO:044114</t>
+          <t>BCIO:044044</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -4526,32 +4422,32 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>communication using formal address</t>
+        </is>
+      </c>
       <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>persuasive communication style</t>
-        </is>
-      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>A communication style which aims to induce or urge the adoption of certain beliefs, theories or lines of action.</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr"/>
+          <t>A communication addressing a person using a formal, legal or official name or title to refer to that person.</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
-      <c r="P117" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>BCIO:044084</t>
+          <t>BCIO:044046</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -4559,153 +4455,135 @@
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>communication using preferred form of address</t>
+        </is>
+      </c>
       <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>autonomy-supportive communication style</t>
-        </is>
-      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>A communication style which aims to promote the recipient's capacity to make their own decisions.</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>from Self-Determination Theory interventions.</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr"/>
+          <t>A communication addressing a person using a name or title that the person has specified the instigator should use.</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>needs-supportive communication style</t>
+          <t>Depending on whether Suzie Jones prefers to be addressed formally, or by her given name, saying either "Hello Mrs Jones" or "Hello Suzie"</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BCIO:044098</t>
+          <t>BCIO:044078</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>shifting focus of communication</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>didactic communication style</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>A communication style characterised by the initiator addressing the recipient in the manner of a teacher or lecturer.</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>gave a short lecture, conference presentation</t>
-        </is>
-      </c>
-      <c r="P119" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication that involves altering the area of greatest attention during the delivery of information.</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>BCIO:044086</t>
+          <t>BCIO:044009</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>active listening</t>
+        </is>
+      </c>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>cold communication style</t>
-        </is>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>A communication style suggesting a lack of human interest or friendliness towards the recipient.</t>
-        </is>
-      </c>
-      <c r="M120" t="inlineStr"/>
+          <t>A communication involving one participant paying close attention to what is said by another, asking questions and reflecting as needed, in an attempt to fully understand what has been said.</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
-      <c r="P120" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BCIO:044099</t>
+          <t>BCIO:044050</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>communication using particular language</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>directive communication style</t>
-        </is>
-      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>A communication style intended to play an active role in another person's decision making.</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>Note that this class is different from direct communication style</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>http://purl.bioontology.org/ontology/MESH/D037001</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication using certain vocabulary or phraseology.</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BCIO:044097</t>
+          <t>BCIO:044056</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -4713,32 +4591,32 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>communication using selected words from a second language</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>conversational communication style</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>A communication style that is typical of interpersonal dialogue which encourages an interactive exchange of ideas and beliefs.</t>
-        </is>
-      </c>
-      <c r="M122" t="inlineStr"/>
+          <t>A communication using occasional words chosen from a language spoken by both the instigator and the recipient that is not the main language.</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BCIO:044120</t>
+          <t>BCIO:044051</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -4746,41 +4624,32 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>communication using neutral language</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>structured communication style</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>A communication style involving the communication content having constituent pre-planned parts.</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>This class is pre-planned style but not to the extent of using a written script. In contrast, "Script-based communication" involves tightly following a set of written instructions.</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr"/>
+          <t>A communication using language in a manner which does not demonstrate an opinion on a particular issue.</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
-      <c r="P123" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q123" t="inlineStr">
-        <is>
-          <t>standardised</t>
-        </is>
-      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BCIO:044102</t>
+          <t>BCIO:044055</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
@@ -4788,32 +4657,32 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>communication avoiding offensive language</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr"/>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>engaging communication style</t>
-        </is>
-      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr">
         <is>
-          <t>A communication style characterised by attempting to attract and maintain a recipient's interest or attention.</t>
-        </is>
-      </c>
-      <c r="M124" t="inlineStr"/>
+          <t>A communication using language chosen by the instigator to avoid using words or phrases that could be perceived as rude or insulting.</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
-      <c r="P124" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>BCIO:044118</t>
+          <t>BCIO:044053</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -4821,37 +4690,32 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>communication using slang</t>
+        </is>
+      </c>
       <c r="H125" t="inlineStr"/>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>responsive communication style</t>
-        </is>
-      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>A communication style characterised by adapting to the views and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>This class is adapting response as a result of how another person is communicating. In contrast, respectful communication style involves showing regard for the feelings etc of others from the outset, but not necessarily adapting one's own communication based on what the other says</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr"/>
+          <t>A communication using informal language shared by members of a particular community.</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BCIO:044091</t>
+          <t>BCIO:044054</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -4859,36 +4723,36 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>communication using specialist language</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>communication style conveying hopefulness</t>
-        </is>
-      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>A communication style which imparts a feeling of optimism that a person will attain a desired outcome.</t>
-        </is>
-      </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="P126" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q126" t="inlineStr">
-        <is>
-          <t>optimism, positivity</t>
-        </is>
-      </c>
+          <t>A communication using words or expressions used by a profession or group that are difficult for others not in that profession or group to understand.</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>using jargon</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>BCIO:044095</t>
+          <t>BCIO:044052</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -4896,139 +4760,141 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>communication using non-pressurising language</t>
+        </is>
+      </c>
       <c r="H127" t="inlineStr"/>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>communication style demonstrating positive regard</t>
-        </is>
-      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>A communication style demonstrating acceptance of everything about the recipient.</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr"/>
+          <t>A communication using language chosen to avoid coercing or persuading the recipient to think, feel or behave in a certain manner.</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BCIO:044101</t>
+          <t>BCIO:044017</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>banter</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr"/>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>empathic communication style</t>
-        </is>
-      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>A communication style which conveys an insightful awareness of the feelings and behaviours of the recipient.</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr"/>
+          <t>A communication involving the exchange of light and teasing remarks intended to be playful.</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Note that teasing is an essential part of the definition of banter. For amusing or enjoyable communication, but without the element of teasing, using entertaining or humourous communication style. Also, note that banter may not always be perceived as playful by the subject of the remarks</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
-      <c r="P128" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q128" t="inlineStr">
-        <is>
-          <t>sensitivity, compassion</t>
-        </is>
-      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>BCIO:044108</t>
+          <t>BCIO:044028</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>communication encouraging discussion</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr"/>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>interactive communication style</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>A communication style characterised by being responsive to the recipient's activity.</t>
-        </is>
-      </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>interactive presentation</t>
-        </is>
-      </c>
-      <c r="P129" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication in which the initiator promotes an extended two-way discussion regarding a topic.</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Contrasts with a more one-way, didactic style</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>BCIO:044110</t>
+          <t>BCIO:050388</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>communication showing acknowledgement</t>
+        </is>
+      </c>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>non-defensive communication style</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
-          <t>A communication style characterised by suggesting the initiator is open to or able to accept criticism.</t>
-        </is>
-      </c>
-      <c r="M130" t="inlineStr"/>
+          <t>A communication involving the expressed recognition of what another has expressed.</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
-      <c r="P130" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BCIO:044087</t>
+          <t>BCIO:044021</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -5036,103 +4902,107 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>communication acknowledging difficulties</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr"/>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>communication style conveying acceptance</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>A communication style that conveys respect and regard for the recipient as an individual.</t>
-        </is>
-      </c>
-      <c r="M131" t="inlineStr"/>
+          <t>A communication showing acknolwedgement conveying empathy or compassion towards a sub-optimal situation or concerns of a recipient.</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr"/>
-      <c r="P131" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BCIO:050381</t>
+          <t>BCIO:044069</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>offering reassurance</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>angry communication style</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>A communication style characterised by anger.</t>
-        </is>
-      </c>
-      <c r="M132" t="inlineStr"/>
+          <t>A communication intended to provide hope and strength in times of anxiety, worry, confusion, grief, distress, or suffering.</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>based on Roter Interactional Analysis System</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>made reassuring statements</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BCIO:044000</t>
+          <t>BCIO:044012</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>asking questions</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr"/>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>behaviour change intervention style of delivery</t>
-        </is>
-      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>A communication style that is an attribute of a BCI content communication process.</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>when a communication style is used as part of a BCI content communication process, then it qualifies as a BCI style of delivery</t>
-        </is>
-      </c>
-      <c r="M133" t="inlineStr"/>
+          <t>A communication in which some participant requests information from another participant.</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>BCIO:044130</t>
+          <t>BCIO:044013</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -5140,36 +5010,32 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>readability</t>
-        </is>
-      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>asking closed-ended questions</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>An attribute of a text used in communication process, concerning the ease of understanding the wording or other qualitative aspects of the text that facilitate comprehension.</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>including adequate blank space and empty circles for the young people and their carers to record and review agenda items</t>
-        </is>
-      </c>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>Asking questions that can only be answered with a limited set of responses.</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BCIO:044129</t>
+          <t>BCIO:050382</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -5177,41 +5043,32 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>object layout</t>
-        </is>
-      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>asking clarifying questions</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>An attribute of an object used in communication process, concerning how the object's components are arranged.</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>the arrangement of components can be deliberately chosen to help communicate intervention content</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>arrangement of chairs in the room for a group intervention, amount of space between blocks of text in a leaflet, arrangement of sections of a website</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>Asking questions in order to better understand an issue.</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BCIO:044125</t>
+          <t>BCIO:044015</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -5219,32 +5076,36 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>tone of voice</t>
-        </is>
-      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>asking leading questions</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>An attribute of an oral communication relating to the rhythm and pitch of what is said.</t>
-        </is>
-      </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>Asking questions designed to prompt the questionee to answer in a specific, pre-determined manner.</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>asking directive questions</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>BCIO:044128</t>
+          <t>BCIO:044014</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -5252,198 +5113,202 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>source visual style</t>
-        </is>
-      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>asking focused questions</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>An attribute of an intervention person source concerning how they appear to others.</t>
-        </is>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>may be purposefully chosen to convey certain attributes of the source</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>Health care professionals' uniform to convey authority and knowledge, doctors not wearing white coats to speak to children</t>
-        </is>
-      </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>Asking questions designed to narrow discussion to focus on a particular aspect or topic.</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>BCIO:050552</t>
+          <t>BCIO:044016</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>communication channel</t>
-        </is>
-      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>asking open-ended questions</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>A &lt;process&gt; by which a communication is delivered.</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr"/>
+          <t>Asking questions that cannot be answered with a simple yes or no, but instead require the questionee to elaborate on their points.</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr"/>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>BCIO:044019</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>planned process</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>discussion</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
-        </is>
-      </c>
+          <t>A communication involving an extended exchange of utterances between an instigator and at least one other person.</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>An utterance is an uninterrupted stretch of speech or writing produced by an individual on a particular occasion. An utterance can range from a single word to a complete sentence.</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BCIO:045000</t>
+          <t>BCIO:044020</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>intervention delivery</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>classroom-style discussion</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>A planned process by which intervention content is delivered.</t>
-        </is>
-      </c>
-      <c r="M140" t="inlineStr"/>
+          <t>A discussion led by the initiator in a manner typical of a teacher or lecturer.</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BCIO:044007</t>
+          <t>BCIO:044024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>participant-led intervention delivery</t>
-        </is>
-      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>communication avoiding argumentation</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
-        </is>
-      </c>
-      <c r="M141" t="inlineStr"/>
+          <t>A communication which aims to focus on the feelings of others without debating the truth or falsity of statements or ideas.</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BCIO:008000</t>
+          <t>BCIO:044071</t>
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>behaviour change intervention delivery</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>reflective communication</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
-        </is>
-      </c>
-      <c r="M142" t="inlineStr"/>
+          <t>A communication presenting a person's previously expressed thoughts and feelings back to them.</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BCIO:044008</t>
+          <t>BCIO:044074</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -5453,7 +5318,7 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>source-led intervention delivery</t>
+          <t>metaphor-using reflective communication</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -5461,22 +5326,26 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A reflective communication in which the instigator  replaces a word or phrase of the recipient's prior assertion with a figure of speech suggesting an analogy.</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>"metaphorical reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>BCIO:044006</t>
+          <t>BCIO:044073</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -5486,7 +5355,7 @@
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>person-centred intervention delivery</t>
+          <t>double-sided reflective communication</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -5494,72 +5363,100 @@
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr">
         <is>
-          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
-        </is>
-      </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A reflective communication in which the instigator aims to highlight both the positive and negative sides of an issue as previously expressed by the recipient.</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>"double-sided reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OGMS:0000060</t>
+          <t>BCIO:044075</t>
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>emotion-emphasising reflective communication</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organsim participates.</t>
-        </is>
-      </c>
+          <t>A reflective communication highlighting the emotional aspects of an issue as previously described by the recipient.</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>"reflection of feeling" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>BCIO:036000</t>
+          <t>BCIO:044072</t>
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>individual human behaviour</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>summarising reflective communication</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>A bodily process of a human that involves co-ordinated contraction of striated muscles controlled by the brain.</t>
-        </is>
-      </c>
+          <t>A reflective communication in which the instigator pulls together key points from a complex story told by the recipient in a succinct restatement.</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>"summarising reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>BCIO:050441</t>
+          <t>BCIO:044076</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -5569,7 +5466,7 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>socially-related behaviour</t>
+          <t>re-evaluation prompting reflective communication</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -5577,113 +5474,138 @@
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr">
         <is>
-          <t>An individual human behaviour that relates to the social environment.</t>
-        </is>
-      </c>
+          <t>A reflective communication in which the instigator restates the recipient's prior assertation in a less credible way to prompt reconsideration of the assertion.</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>"amplified reflection" in Motivational Interviewing</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BCIO:036025</t>
+          <t>BCIO:044124</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>relationship building</t>
+        </is>
+      </c>
       <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>inter-personal behaviour</t>
-        </is>
-      </c>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr">
         <is>
-          <t>An &lt;socially-related behaviour&gt; that involves an interaction between two or more people.</t>
-        </is>
-      </c>
-      <c r="M148" t="inlineStr"/>
+          <t>A communication aimed at building or managing aspects of the interpersonal relationship between an initiator and a recipient rather than focusing on delivering communication content.</t>
+        </is>
+      </c>
       <c r="N148" t="inlineStr"/>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>offering contact, inviting patient to contact you in the event of difficulties or questions</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BCIO:036034</t>
+          <t>BCIO:044047</t>
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>communication using commands</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>human communication behaviour</t>
-        </is>
-      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>An expressive behaviour that involves the transmission of information between two or more people.</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication using statements that order or direct a person to think or behave in a certain way.</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>communication using imperatives</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BCIO:050237</t>
+          <t>BCIO:044001</t>
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>intervention content communication process</t>
+        </is>
+      </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>linguistic communication behaviour</t>
-        </is>
-      </c>
+      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>A human communication behaviour in which the information that is communicated is encoded in language.</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr"/>
+          <t>A communication that transmits the content of an intervention</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Note that an intervention is a planned process with the aim of influencing some outcome whereas a behaviour change intervention is an intervention that aims to influence human behaviour as an outcome.</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BCIO:050457</t>
+          <t>BCIO:044002</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
@@ -5693,7 +5615,7 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>expressive behaviour</t>
+          <t>behaviour change intervention content communication process</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -5701,130 +5623,180 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>An individual human behaviour that conveys a thought or feeling.</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr"/>
+          <t>An intervention content communication process that is about behaviour change intervention content</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>A behaviour change intervention is a planned process that aims to influence human behaviour.  In contrast, an intervention is a planned process with the aim of influencing some outcome.  This outcome may be other than human behaviour.</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BCIO:050374</t>
+          <t>BCIO:044029</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>communication evoking another's ideas about change</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>laughing</t>
-        </is>
-      </c>
+      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>An expressive behaviour showing elation, amusement or scorn by means of facial expressions and repeated sharp exhalations.</t>
-        </is>
-      </c>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+          <t>A communication in which the initiator attempts to elicit the recipient’s own thoughts and ideas about change rather than imposing the initiator’s own opinion.</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>evoking change talk in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BFO:0000002</t>
+          <t>BCIO:044049</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>continuant</t>
-        </is>
-      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>communication using interjections to signal attentiveness</t>
+        </is>
+      </c>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>An entity that exists in full at any time in which it exists at all, persists through time while maintaining its identity and has no temporal parts.</t>
+          <t>A communication in which one person uses brief interjections to signal that they are listening to what the other person is saying.</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>An interjection is a word, phrase or exclamation which is typically unconnected to a sentence and is used to express an emotion or reaction.</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>"Back-channels" or "undertalk" in the Roter Interaction Analysis System</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Words like "interesting", "yeah"," mmhmm"</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BFO:0000031</t>
+          <t>BCIO:044037</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>communication involving agreement</t>
+        </is>
+      </c>
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
-        </is>
-      </c>
+          <t>A communication in which one participant concurs with the views stated by another.</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>IAO:0000030</t>
+          <t>BCIO:044038</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr"/>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
+      <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr"/>
-      <c r="G155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>communication involving agreement followed by highlighting incongruent aspects</t>
+        </is>
+      </c>
       <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>A generically dependent continuant that is about some thing.</t>
-        </is>
-      </c>
+          <t>A communication involving agreement in which one participant concurs with the views stated by another and then points out an incongruent aspect of the situation under discussion.</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>"agreement with a twist" in motivational interviewing</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BCIO:050555</t>
+          <t>BCIO:044060</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -5833,7 +5805,7 @@
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>communication message</t>
+          <t>guiding communication</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -5842,32 +5814,36 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>An &lt;information content entity&gt; transmitted from a communication source to a communication recipient.</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr"/>
+          <t>A communication that involves suggesting adoption of certain beliefs, theories or lines of action by others.</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>When a practitioner suggests to a patient 'Could you think about it like this...'</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>BFO:0000004</t>
+          <t>OBI:0000011</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="inlineStr"/>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>independent continuant</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>planned process</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr"/>
@@ -5875,97 +5851,113 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
+          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BFO:0000040</t>
+          <t>BCIO:045000</t>
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>intervention delivery</t>
+        </is>
+      </c>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>An independent continuant that is spatially extended whose identity is independent of that of other entities and can be maintained through time.</t>
-        </is>
-      </c>
+          <t>A planned process by which intervention content is delivered.</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BCIO:050554</t>
+          <t>BCIO:044008</t>
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>communication source</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>source-led intervention delivery</t>
+        </is>
+      </c>
       <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>A &lt;material entity&gt; that originates a communication.</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr"/>
+          <t>An intervention delivery in which the intervention person source takes the lead in determining the focus of the intervention.</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OGMS:0000087</t>
+          <t>BCIO:044006</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>extended organism</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>person-centred intervention delivery</t>
+        </is>
+      </c>
       <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>An object aggregate consisting of an organism and all material entities located within the organism, overlapping the organism, or occupying sites formed in part by the organism.</t>
-        </is>
-      </c>
+          <t>An intervention delivery characterised by efforts by an intervention source to give a person the resources they need to manage their own life and make them an active participant in deciding how to move forward.</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MF:0000016</t>
+          <t>BCIO:044007</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -5975,7 +5967,7 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>human being</t>
+          <t>participant-led intervention delivery</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -5983,14 +5975,22 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>An extended organism that is a member of the species Homo sapiens.</t>
-        </is>
-      </c>
+          <t>An intervention delivery in which the participant takes the lead in determining the focus of the intervention.</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>BCIO:050553</t>
+          <t>BCIO:008000</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -5998,26 +5998,26 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>communication recipient</t>
-        </is>
-      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>behaviour change intervention delivery</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>A &lt;person&gt; who receives a communication.</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr"/>
+          <t>An intervention delivery in which the intervention is a behaviour change intervention.</t>
+        </is>
+      </c>
       <c r="N162" t="inlineStr"/>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>style of delivery</t>
-        </is>
-      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>style of delivery</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
     </row>
   </sheetData>

--- a/StyleOfDelivery/BCIO-style-hierarchy.xlsx
+++ b/StyleOfDelivery/BCIO-style-hierarchy.xlsx
@@ -567,7 +567,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>A continuant that is dependent on one or other independent continuant bearers. For every instance of A requires some instance of (an independent continuant type) B but which instance of B serves can change from time to time.</t>
+          <t>b is a generically dependent continuant = Def. b is a continuant that g-depends_on one or more other entities. (axiom label in BFO2 Reference: [074-001])</t>
         </is>
       </c>
     </row>
@@ -650,7 +650,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>b is an independent continuant = Def. b is a continuant which is such that there is no c and no t such that b s-depends_on c at t. (axiom label in BFO2 Reference: [017-002])</t>
+          <t>A continuant that is a bearer of quality and realizable entity entities, in which other entities inhere and which itself cannot inhere in anything.</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>person</t>
+          <t>human being</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -841,7 +841,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>p is a process = Def. p is an occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t. (axiom label in BFO2 Reference: [083-003])</t>
+          <t>An occurrent that has temporal proper parts and for some time t, p s-depends_on some material entity at t.</t>
         </is>
       </c>
     </row>
@@ -3030,7 +3030,7 @@
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>A process in which at least one bodily component of an organism participates.</t>
+          <t>A process in which at least one bodily component of an organsim participates.</t>
         </is>
       </c>
     </row>
